--- a/praktikumsplaner-backend/src/main/resources-non-filtered/templates/ITM_IT_POR.xlsx
+++ b/praktikumsplaner-backend/src/main/resources-non-filtered/templates/ITM_IT_POR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Intern\I-POR221\07_Praktikumsplatzmanagement\01_PP_Orga\01_PP_Abfragen\IT\2026_03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A662888E-0CC7-4207-A848-0FCF9E02FF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADDB81C-9F64-4A74-B3E1-AA352F9297D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{ECF369DD-E939-4FB1-9EAA-B3EEB7A3D364}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{ECF369DD-E939-4FB1-9EAA-B3EEB7A3D364}"/>
   </bookViews>
   <sheets>
     <sheet name="Drop Down" sheetId="4" state="hidden" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Legende" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QE2'!$A$1:$Q$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QE2'!$A$1:$R$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QE3'!$A$1:$R$103</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="97">
   <si>
     <t>Referat</t>
   </si>
@@ -495,6 +495,24 @@
   <si>
     <t>BWI</t>
   </si>
+  <si>
+    <t>Zwingende Angabe "Ja" oder "Nein"</t>
+  </si>
+  <si>
+    <r>
+      <t>Projektarbeit möglich</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -730,7 +748,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -903,15 +921,6 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -942,13 +951,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{9C6AEE93-3A70-47F8-A32D-8685AF62D698}"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -971,34 +1006,6 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1361,16 +1368,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B1A642-8A93-4EE4-BB9D-ED8CDCF54088}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="11" style="4"/>
     <col min="5" max="5" width="15" style="4" customWidth="1"/>
     <col min="6" max="6" width="11" style="4"/>
-    <col min="7" max="7" width="16.4140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="16.375" style="4" customWidth="1"/>
     <col min="8" max="16384" width="11" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1396,7 +1403,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>18</v>
       </c>
@@ -1422,7 +1429,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -1448,7 +1455,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
@@ -1462,107 +1469,107 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>50</v>
       </c>
@@ -1575,29 +1582,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{769FA850-14D9-4FA2-A099-BA408AF52616}">
-  <dimension ref="A1:R205"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.08203125" defaultRowHeight="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S205"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.125" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.08203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="1" customWidth="1"/>
     <col min="4" max="5" width="26" style="48" customWidth="1"/>
-    <col min="6" max="6" width="30.58203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="48.08203125" style="48" customWidth="1"/>
-    <col min="8" max="8" width="72.08203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="92.58203125" style="48" customWidth="1"/>
-    <col min="10" max="10" width="31.58203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="28" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="33.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="37.08203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="23.08203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="24.75" style="1" customWidth="1"/>
-    <col min="17" max="17" width="16.25" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="11.08203125" style="1"/>
+    <col min="6" max="6" width="30.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="48.125" style="48" customWidth="1"/>
+    <col min="8" max="8" width="72.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="92.625" style="48" customWidth="1"/>
+    <col min="10" max="10" width="15.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="31.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="28" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16.625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="33.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="37.125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="23.125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="24.75" style="1" customWidth="1"/>
+    <col min="18" max="18" width="16.25" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="11.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1625,32 +1633,35 @@
       <c r="I1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="4" customFormat="1" ht="154.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" s="4" customFormat="1" ht="165.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>4</v>
@@ -1658,13 +1669,13 @@
       <c r="C2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="51" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="47" t="s">
@@ -1673,83 +1684,89 @@
       <c r="H2" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="52" t="s">
+      <c r="J2" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="K2" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="52" t="s">
+      <c r="L2" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="52" t="s">
+      <c r="N2" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>40</v>
       </c>
       <c r="P2" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="56" customFormat="1" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:19" s="53" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="I3" s="53" t="s">
+      <c r="I3" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="J3" s="53" t="s">
+      <c r="J3" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="53" t="s">
+      <c r="K3" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="L3" s="53" t="s">
+      <c r="M3" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="53" t="s">
+      <c r="N3" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="N3" s="53" t="s">
+      <c r="O3" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="59"/>
-    </row>
-    <row r="4" spans="1:18" s="8" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="56"/>
+    </row>
+    <row r="4" spans="1:19" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1759,16 +1776,17 @@
       <c r="G4" s="48"/>
       <c r="H4" s="6"/>
       <c r="I4" s="48"/>
-      <c r="J4" s="6"/>
+      <c r="J4" s="62"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
-      <c r="O4" s="7"/>
+      <c r="O4" s="6"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
-    </row>
-    <row r="5" spans="1:18" s="8" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="R4" s="7"/>
+    </row>
+    <row r="5" spans="1:19" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -1778,16 +1796,17 @@
       <c r="G5" s="48"/>
       <c r="H5" s="6"/>
       <c r="I5" s="48"/>
-      <c r="J5" s="6"/>
+      <c r="J5" s="62"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="7"/>
+      <c r="O5" s="6"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
-    </row>
-    <row r="6" spans="1:18" s="8" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="R5" s="7"/>
+    </row>
+    <row r="6" spans="1:19" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -1797,16 +1816,17 @@
       <c r="G6" s="48"/>
       <c r="H6" s="6"/>
       <c r="I6" s="48"/>
-      <c r="J6" s="6"/>
+      <c r="J6" s="62"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="10"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-    </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="R6" s="6"/>
+    </row>
+    <row r="7" spans="1:19" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1815,16 +1835,17 @@
       <c r="G7" s="48"/>
       <c r="H7" s="6"/>
       <c r="I7" s="48"/>
-      <c r="J7" s="6"/>
+      <c r="J7" s="62"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="12"/>
+      <c r="O7" s="6"/>
       <c r="P7" s="12"/>
       <c r="Q7" s="12"/>
-    </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="R7" s="12"/>
+    </row>
+    <row r="8" spans="1:19" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="11"/>
       <c r="C8" s="13"/>
@@ -1834,17 +1855,18 @@
       <c r="G8" s="48"/>
       <c r="H8" s="11"/>
       <c r="I8" s="48"/>
-      <c r="J8" s="6"/>
+      <c r="J8" s="62"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="11"/>
+      <c r="O8" s="6"/>
       <c r="P8" s="11"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="2"/>
-    </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q8" s="11"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="2"/>
+    </row>
+    <row r="9" spans="1:19" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="11"/>
       <c r="C9" s="13"/>
@@ -1854,17 +1876,18 @@
       <c r="G9" s="48"/>
       <c r="H9" s="11"/>
       <c r="I9" s="48"/>
-      <c r="J9" s="6"/>
+      <c r="J9" s="62"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="13"/>
+      <c r="O9" s="6"/>
       <c r="P9" s="13"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="2"/>
-    </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q9" s="13"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="2"/>
+    </row>
+    <row r="10" spans="1:19" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1873,17 +1896,18 @@
       <c r="G10" s="48"/>
       <c r="H10" s="11"/>
       <c r="I10" s="48"/>
-      <c r="J10" s="6"/>
+      <c r="J10" s="62"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="13"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="11"/>
       <c r="P10" s="13"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="2"/>
-    </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q10" s="13"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -1892,16 +1916,17 @@
       <c r="G11" s="48"/>
       <c r="H11" s="11"/>
       <c r="I11" s="48"/>
-      <c r="J11" s="6"/>
+      <c r="J11" s="62"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="13"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="11"/>
       <c r="P11" s="13"/>
-      <c r="Q11" s="15"/>
-    </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q11" s="13"/>
+      <c r="R11" s="15"/>
+    </row>
+    <row r="12" spans="1:19" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1911,16 +1936,17 @@
       <c r="G12" s="48"/>
       <c r="H12" s="11"/>
       <c r="I12" s="48"/>
-      <c r="J12" s="6"/>
+      <c r="J12" s="62"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="14"/>
-    </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="O12" s="6"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="14"/>
+    </row>
+    <row r="13" spans="1:19" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1930,16 +1956,17 @@
       <c r="G13" s="48"/>
       <c r="H13" s="11"/>
       <c r="I13" s="48"/>
-      <c r="J13" s="6"/>
+      <c r="J13" s="62"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="14"/>
-    </row>
-    <row r="14" spans="1:18" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="O13" s="6"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="14"/>
+    </row>
+    <row r="14" spans="1:19" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -1949,17 +1976,18 @@
       <c r="G14" s="48"/>
       <c r="H14" s="11"/>
       <c r="I14" s="48"/>
-      <c r="J14" s="6"/>
+      <c r="J14" s="62"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="9"/>
-    </row>
-    <row r="15" spans="1:18" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="O14" s="6"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="9"/>
+    </row>
+    <row r="15" spans="1:19" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -1968,17 +1996,18 @@
       <c r="G15" s="48"/>
       <c r="H15" s="11"/>
       <c r="I15" s="48"/>
-      <c r="J15" s="6"/>
+      <c r="J15" s="62"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="16"/>
-    </row>
-    <row r="16" spans="1:18" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="O15" s="6"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="16"/>
+    </row>
+    <row r="16" spans="1:19" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -1988,17 +2017,18 @@
       <c r="G16" s="48"/>
       <c r="H16" s="17"/>
       <c r="I16" s="48"/>
-      <c r="J16" s="6"/>
+      <c r="J16" s="62"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
-      <c r="O16" s="11"/>
+      <c r="O16" s="6"/>
       <c r="P16" s="11"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="16"/>
-    </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q16" s="11"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="16"/>
+    </row>
+    <row r="17" spans="1:19" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -2007,17 +2037,18 @@
       <c r="G17" s="48"/>
       <c r="H17" s="17"/>
       <c r="I17" s="48"/>
-      <c r="J17" s="6"/>
+      <c r="J17" s="62"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
-      <c r="O17" s="11"/>
+      <c r="O17" s="6"/>
       <c r="P17" s="11"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="16"/>
-    </row>
-    <row r="18" spans="1:18" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q17" s="11"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="16"/>
+    </row>
+    <row r="18" spans="1:19" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -2027,17 +2058,18 @@
       <c r="G18" s="48"/>
       <c r="H18" s="17"/>
       <c r="I18" s="48"/>
-      <c r="J18" s="6"/>
+      <c r="J18" s="62"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
-      <c r="O18" s="11"/>
+      <c r="O18" s="6"/>
       <c r="P18" s="11"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="16"/>
-    </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q18" s="11"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="16"/>
+    </row>
+    <row r="19" spans="1:19" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -2046,17 +2078,18 @@
       <c r="G19" s="48"/>
       <c r="H19" s="11"/>
       <c r="I19" s="48"/>
-      <c r="J19" s="6"/>
+      <c r="J19" s="62"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
-      <c r="O19" s="11"/>
+      <c r="O19" s="6"/>
       <c r="P19" s="11"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="8"/>
-    </row>
-    <row r="20" spans="1:18" s="16" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q19" s="11"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="8"/>
+    </row>
+    <row r="20" spans="1:19" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2066,17 +2099,18 @@
       <c r="G20" s="48"/>
       <c r="H20" s="11"/>
       <c r="I20" s="48"/>
-      <c r="J20" s="6"/>
+      <c r="J20" s="62"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
-      <c r="O20" s="13"/>
+      <c r="O20" s="6"/>
       <c r="P20" s="13"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="9"/>
-    </row>
-    <row r="21" spans="1:18" s="16" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q20" s="13"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="9"/>
+    </row>
+    <row r="21" spans="1:19" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -2086,17 +2120,18 @@
       <c r="G21" s="48"/>
       <c r="H21" s="11"/>
       <c r="I21" s="48"/>
-      <c r="J21" s="6"/>
+      <c r="J21" s="62"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
-      <c r="O21" s="11"/>
+      <c r="O21" s="6"/>
       <c r="P21" s="11"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="2"/>
-    </row>
-    <row r="22" spans="1:18" s="16" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q21" s="11"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="2"/>
+    </row>
+    <row r="22" spans="1:19" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -2106,16 +2141,17 @@
       <c r="G22" s="48"/>
       <c r="H22" s="11"/>
       <c r="I22" s="48"/>
-      <c r="J22" s="6"/>
+      <c r="J22" s="62"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
-      <c r="O22" s="13"/>
+      <c r="O22" s="6"/>
       <c r="P22" s="13"/>
-      <c r="Q22" s="15"/>
-    </row>
-    <row r="23" spans="1:18" s="16" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q22" s="13"/>
+      <c r="R22" s="15"/>
+    </row>
+    <row r="23" spans="1:19" s="16" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2125,17 +2161,18 @@
       <c r="G23" s="48"/>
       <c r="H23" s="11"/>
       <c r="I23" s="48"/>
-      <c r="J23" s="6"/>
+      <c r="J23" s="62"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
-      <c r="O23" s="11"/>
+      <c r="O23" s="6"/>
       <c r="P23" s="11"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="9"/>
-    </row>
-    <row r="24" spans="1:18" s="16" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q23" s="11"/>
+      <c r="R23" s="14"/>
+      <c r="S23" s="9"/>
+    </row>
+    <row r="24" spans="1:19" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2145,16 +2182,17 @@
       <c r="G24" s="48"/>
       <c r="H24" s="11"/>
       <c r="I24" s="48"/>
-      <c r="J24" s="6"/>
+      <c r="J24" s="62"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
-      <c r="O24" s="11"/>
+      <c r="O24" s="6"/>
       <c r="P24" s="11"/>
-      <c r="Q24" s="14"/>
-    </row>
-    <row r="25" spans="1:18" s="8" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q24" s="11"/>
+      <c r="R24" s="14"/>
+    </row>
+    <row r="25" spans="1:19" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="11"/>
       <c r="C25" s="13"/>
@@ -2164,17 +2202,18 @@
       <c r="G25" s="48"/>
       <c r="H25" s="11"/>
       <c r="I25" s="48"/>
-      <c r="J25" s="6"/>
+      <c r="J25" s="62"/>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="9"/>
-    </row>
-    <row r="26" spans="1:18" s="16" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="O25" s="6"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="9"/>
+    </row>
+    <row r="26" spans="1:19" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2184,17 +2223,18 @@
       <c r="G26" s="48"/>
       <c r="H26" s="11"/>
       <c r="I26" s="48"/>
-      <c r="J26" s="6"/>
+      <c r="J26" s="62"/>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
-      <c r="O26" s="11"/>
+      <c r="O26" s="6"/>
       <c r="P26" s="11"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="9"/>
-    </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q26" s="11"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="9"/>
+    </row>
+    <row r="27" spans="1:19" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2203,16 +2243,17 @@
       <c r="G27" s="48"/>
       <c r="H27" s="11"/>
       <c r="I27" s="48"/>
-      <c r="J27" s="6"/>
+      <c r="J27" s="62"/>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
-      <c r="O27" s="11"/>
+      <c r="O27" s="6"/>
       <c r="P27" s="11"/>
-      <c r="Q27" s="14"/>
-    </row>
-    <row r="28" spans="1:18" s="8" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+      <c r="Q27" s="11"/>
+      <c r="R27" s="14"/>
+    </row>
+    <row r="28" spans="1:19" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2222,1420 +2263,1603 @@
       <c r="G28" s="48"/>
       <c r="H28" s="11"/>
       <c r="I28" s="48"/>
-      <c r="J28" s="6"/>
+      <c r="J28" s="62"/>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
-      <c r="O28" s="11"/>
+      <c r="O28" s="6"/>
       <c r="P28" s="11"/>
-      <c r="Q28" s="14"/>
-    </row>
-    <row r="29" spans="1:18" s="8" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q28" s="11"/>
+      <c r="R28" s="14"/>
+    </row>
+    <row r="29" spans="1:19" s="8" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="D29" s="48"/>
       <c r="E29" s="48"/>
       <c r="F29" s="21"/>
       <c r="G29" s="48"/>
       <c r="I29" s="48"/>
-      <c r="J29" s="6"/>
+      <c r="J29" s="62"/>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
-    </row>
-    <row r="30" spans="1:18" s="8" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:19" s="8" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="D30" s="48"/>
       <c r="E30" s="48"/>
       <c r="F30" s="9"/>
       <c r="G30" s="48"/>
       <c r="I30" s="48"/>
-      <c r="J30" s="6"/>
+      <c r="J30" s="62"/>
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
-    </row>
-    <row r="31" spans="1:18" s="8" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31" spans="1:19" s="8" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
       <c r="D31" s="48"/>
       <c r="E31" s="48"/>
       <c r="F31" s="9"/>
       <c r="G31" s="48"/>
       <c r="I31" s="48"/>
-      <c r="J31" s="6"/>
+      <c r="J31" s="62"/>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
-    </row>
-    <row r="32" spans="1:18" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="1:19" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
       <c r="F32" s="9"/>
-      <c r="J32" s="6"/>
+      <c r="J32" s="62"/>
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
-    </row>
-    <row r="33" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N32" s="6"/>
+    </row>
+    <row r="33" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
       <c r="F33" s="8"/>
-      <c r="J33" s="6"/>
+      <c r="J33" s="62"/>
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
-    </row>
-    <row r="34" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
       <c r="F34" s="9"/>
-      <c r="J34" s="6"/>
+      <c r="J34" s="62"/>
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
-    </row>
-    <row r="35" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="F35" s="9"/>
-      <c r="J35" s="6"/>
+      <c r="J35" s="62"/>
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
-    </row>
-    <row r="36" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
       <c r="F36" s="21"/>
-      <c r="J36" s="6"/>
+      <c r="J36" s="62"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
-    </row>
-    <row r="37" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
       <c r="F37" s="9"/>
-      <c r="J37" s="6"/>
+      <c r="J37" s="62"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
-    </row>
-    <row r="38" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N37" s="6"/>
+    </row>
+    <row r="38" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
       <c r="F38" s="9"/>
-      <c r="J38" s="6"/>
+      <c r="J38" s="62"/>
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
-    </row>
-    <row r="39" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N38" s="6"/>
+    </row>
+    <row r="39" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="F39" s="9"/>
-      <c r="J39" s="6"/>
+      <c r="J39" s="62"/>
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
-    </row>
-    <row r="40" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N39" s="6"/>
+    </row>
+    <row r="40" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6"/>
       <c r="F40" s="9"/>
-      <c r="J40" s="6"/>
+      <c r="J40" s="62"/>
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
-    </row>
-    <row r="41" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N40" s="6"/>
+    </row>
+    <row r="41" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
       <c r="F41" s="21"/>
-      <c r="J41" s="6"/>
+      <c r="J41" s="62"/>
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
-    </row>
-    <row r="42" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N41" s="6"/>
+    </row>
+    <row r="42" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
       <c r="F42" s="9"/>
-      <c r="J42" s="6"/>
+      <c r="J42" s="62"/>
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
-    </row>
-    <row r="43" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N42" s="6"/>
+    </row>
+    <row r="43" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
       <c r="F43" s="9"/>
-      <c r="J43" s="6"/>
+      <c r="J43" s="62"/>
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
-    </row>
-    <row r="44" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N43" s="6"/>
+    </row>
+    <row r="44" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
       <c r="F44" s="9"/>
-      <c r="J44" s="6"/>
+      <c r="J44" s="62"/>
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
-    </row>
-    <row r="45" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N44" s="6"/>
+    </row>
+    <row r="45" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="F45" s="9"/>
-      <c r="J45" s="6"/>
+      <c r="J45" s="62"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
-    </row>
-    <row r="46" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N45" s="6"/>
+    </row>
+    <row r="46" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="F46" s="8"/>
-      <c r="J46" s="6"/>
+      <c r="J46" s="62"/>
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
-    </row>
-    <row r="47" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N46" s="6"/>
+    </row>
+    <row r="47" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6"/>
       <c r="F47" s="2"/>
-      <c r="J47" s="6"/>
+      <c r="J47" s="62"/>
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
-    </row>
-    <row r="48" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N47" s="6"/>
+    </row>
+    <row r="48" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
       <c r="F48" s="9"/>
-      <c r="J48" s="6"/>
+      <c r="J48" s="62"/>
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
-    </row>
-    <row r="49" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N48" s="6"/>
+    </row>
+    <row r="49" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
       <c r="F49" s="9"/>
-      <c r="J49" s="6"/>
+      <c r="J49" s="62"/>
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
-    </row>
-    <row r="50" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N49" s="6"/>
+    </row>
+    <row r="50" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6"/>
       <c r="F50" s="9"/>
-      <c r="J50" s="6"/>
+      <c r="J50" s="62"/>
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
-    </row>
-    <row r="51" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N50" s="6"/>
+    </row>
+    <row r="51" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
       <c r="F51" s="9"/>
-      <c r="J51" s="6"/>
+      <c r="J51" s="62"/>
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
-    </row>
-    <row r="52" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N51" s="6"/>
+    </row>
+    <row r="52" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6"/>
       <c r="F52" s="9"/>
-      <c r="J52" s="6"/>
+      <c r="J52" s="62"/>
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
-    </row>
-    <row r="53" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N52" s="6"/>
+    </row>
+    <row r="53" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6"/>
       <c r="F53" s="21"/>
-      <c r="J53" s="6"/>
+      <c r="J53" s="62"/>
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
-    </row>
-    <row r="54" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N53" s="6"/>
+    </row>
+    <row r="54" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
       <c r="F54" s="9"/>
-      <c r="J54" s="6"/>
+      <c r="J54" s="62"/>
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
-    </row>
-    <row r="55" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N54" s="6"/>
+    </row>
+    <row r="55" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
       <c r="F55" s="9"/>
-      <c r="J55" s="6"/>
+      <c r="J55" s="62"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
-    </row>
-    <row r="56" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N55" s="6"/>
+    </row>
+    <row r="56" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6"/>
       <c r="F56" s="9"/>
-      <c r="J56" s="6"/>
+      <c r="J56" s="62"/>
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
-    </row>
-    <row r="57" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N56" s="6"/>
+    </row>
+    <row r="57" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
       <c r="F57" s="9"/>
-      <c r="J57" s="6"/>
+      <c r="J57" s="62"/>
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
-    </row>
-    <row r="58" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N57" s="6"/>
+    </row>
+    <row r="58" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6"/>
       <c r="F58" s="9"/>
-      <c r="J58" s="6"/>
+      <c r="J58" s="62"/>
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
-    </row>
-    <row r="59" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N58" s="6"/>
+    </row>
+    <row r="59" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6"/>
       <c r="F59" s="9"/>
-      <c r="J59" s="6"/>
+      <c r="J59" s="62"/>
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
-    </row>
-    <row r="60" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N59" s="6"/>
+    </row>
+    <row r="60" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6"/>
       <c r="F60" s="9"/>
-      <c r="J60" s="6"/>
+      <c r="J60" s="62"/>
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
-    </row>
-    <row r="61" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N60" s="6"/>
+    </row>
+    <row r="61" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
       <c r="F61" s="9"/>
-      <c r="J61" s="6"/>
+      <c r="J61" s="62"/>
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
-    </row>
-    <row r="62" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N61" s="6"/>
+    </row>
+    <row r="62" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6"/>
       <c r="F62" s="9"/>
-      <c r="J62" s="6"/>
+      <c r="J62" s="62"/>
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
-    </row>
-    <row r="63" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N62" s="6"/>
+    </row>
+    <row r="63" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6"/>
       <c r="F63" s="9"/>
-      <c r="J63" s="6"/>
+      <c r="J63" s="62"/>
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
-    </row>
-    <row r="64" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N63" s="6"/>
+    </row>
+    <row r="64" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6"/>
       <c r="F64" s="9"/>
-      <c r="J64" s="6"/>
+      <c r="J64" s="62"/>
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
-    </row>
-    <row r="65" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N64" s="6"/>
+    </row>
+    <row r="65" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6"/>
       <c r="F65" s="9"/>
-      <c r="J65" s="6"/>
+      <c r="J65" s="62"/>
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
-    </row>
-    <row r="66" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N65" s="6"/>
+    </row>
+    <row r="66" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6"/>
       <c r="F66" s="9"/>
-      <c r="J66" s="6"/>
+      <c r="J66" s="62"/>
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
-    </row>
-    <row r="67" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N66" s="6"/>
+    </row>
+    <row r="67" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6"/>
       <c r="F67" s="2"/>
-      <c r="J67" s="6"/>
+      <c r="J67" s="62"/>
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
-    </row>
-    <row r="68" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N67" s="6"/>
+    </row>
+    <row r="68" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
       <c r="F68" s="9"/>
-      <c r="J68" s="6"/>
+      <c r="J68" s="62"/>
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
-    </row>
-    <row r="69" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N68" s="6"/>
+    </row>
+    <row r="69" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6"/>
       <c r="F69" s="2"/>
-      <c r="J69" s="6"/>
+      <c r="J69" s="62"/>
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
-    </row>
-    <row r="70" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6"/>
       <c r="F70" s="2"/>
-      <c r="J70" s="6"/>
+      <c r="J70" s="62"/>
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
-    </row>
-    <row r="71" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N70" s="6"/>
+    </row>
+    <row r="71" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
       <c r="F71" s="2"/>
-      <c r="J71" s="6"/>
+      <c r="J71" s="62"/>
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
-    </row>
-    <row r="72" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N71" s="6"/>
+    </row>
+    <row r="72" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6"/>
       <c r="F72" s="2"/>
-      <c r="J72" s="6"/>
+      <c r="J72" s="62"/>
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
-    </row>
-    <row r="73" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N72" s="6"/>
+    </row>
+    <row r="73" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6"/>
       <c r="F73" s="9"/>
-      <c r="J73" s="6"/>
+      <c r="J73" s="62"/>
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
-    </row>
-    <row r="74" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N73" s="6"/>
+    </row>
+    <row r="74" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6"/>
       <c r="F74" s="9"/>
-      <c r="J74" s="6"/>
+      <c r="J74" s="62"/>
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
-    </row>
-    <row r="75" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N74" s="6"/>
+    </row>
+    <row r="75" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6"/>
       <c r="F75" s="9"/>
-      <c r="J75" s="6"/>
+      <c r="J75" s="62"/>
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
-    </row>
-    <row r="76" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N75" s="6"/>
+    </row>
+    <row r="76" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6"/>
       <c r="F76" s="9"/>
-      <c r="J76" s="6"/>
+      <c r="J76" s="62"/>
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
-    </row>
-    <row r="77" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N76" s="6"/>
+    </row>
+    <row r="77" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
       <c r="F77" s="21"/>
-      <c r="J77" s="6"/>
+      <c r="J77" s="62"/>
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
-    </row>
-    <row r="78" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N77" s="6"/>
+    </row>
+    <row r="78" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6"/>
       <c r="F78" s="9"/>
-      <c r="J78" s="6"/>
+      <c r="J78" s="62"/>
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
-    </row>
-    <row r="79" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N78" s="6"/>
+    </row>
+    <row r="79" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6"/>
       <c r="F79" s="9"/>
-      <c r="J79" s="6"/>
+      <c r="J79" s="62"/>
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
-    </row>
-    <row r="80" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N79" s="6"/>
+    </row>
+    <row r="80" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6"/>
       <c r="F80" s="9"/>
-      <c r="J80" s="6"/>
+      <c r="J80" s="62"/>
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
-    </row>
-    <row r="81" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N80" s="6"/>
+    </row>
+    <row r="81" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6"/>
       <c r="F81" s="21"/>
-      <c r="J81" s="6"/>
+      <c r="J81" s="62"/>
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
-    </row>
-    <row r="82" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N81" s="6"/>
+    </row>
+    <row r="82" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6"/>
       <c r="F82" s="21"/>
-      <c r="J82" s="6"/>
+      <c r="J82" s="62"/>
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
-    </row>
-    <row r="83" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N82" s="6"/>
+    </row>
+    <row r="83" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6"/>
       <c r="F83" s="9"/>
-      <c r="J83" s="6"/>
+      <c r="J83" s="62"/>
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
-    </row>
-    <row r="84" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N83" s="6"/>
+    </row>
+    <row r="84" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6"/>
       <c r="F84" s="9"/>
-      <c r="J84" s="6"/>
+      <c r="J84" s="62"/>
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
-    </row>
-    <row r="85" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N84" s="6"/>
+    </row>
+    <row r="85" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6"/>
       <c r="F85" s="6"/>
-      <c r="J85" s="6"/>
+      <c r="J85" s="62"/>
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
-    </row>
-    <row r="86" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N85" s="6"/>
+    </row>
+    <row r="86" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6"/>
       <c r="F86" s="16"/>
-      <c r="J86" s="6"/>
+      <c r="J86" s="62"/>
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
-    </row>
-    <row r="87" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N86" s="6"/>
+    </row>
+    <row r="87" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6"/>
       <c r="F87" s="6"/>
-      <c r="J87" s="6"/>
+      <c r="J87" s="62"/>
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
-    </row>
-    <row r="88" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N87" s="6"/>
+    </row>
+    <row r="88" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6"/>
       <c r="F88" s="11"/>
-      <c r="J88" s="6"/>
+      <c r="J88" s="62"/>
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
-    </row>
-    <row r="89" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N88" s="6"/>
+    </row>
+    <row r="89" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6"/>
       <c r="F89" s="18"/>
-      <c r="J89" s="6"/>
+      <c r="J89" s="62"/>
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
-    </row>
-    <row r="90" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N89" s="6"/>
+    </row>
+    <row r="90" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6"/>
       <c r="F90" s="8"/>
-      <c r="J90" s="6"/>
+      <c r="J90" s="62"/>
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
-    </row>
-    <row r="91" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N90" s="6"/>
+    </row>
+    <row r="91" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6"/>
       <c r="F91" s="10"/>
-      <c r="J91" s="6"/>
+      <c r="J91" s="62"/>
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
-    </row>
-    <row r="92" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N91" s="6"/>
+    </row>
+    <row r="92" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6"/>
       <c r="F92" s="6"/>
-      <c r="J92" s="6"/>
+      <c r="J92" s="62"/>
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
-    </row>
-    <row r="93" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N92" s="6"/>
+    </row>
+    <row r="93" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6"/>
       <c r="F93" s="12"/>
-      <c r="J93" s="6"/>
+      <c r="J93" s="62"/>
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
-    </row>
-    <row r="94" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N93" s="6"/>
+    </row>
+    <row r="94" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6"/>
       <c r="F94" s="6"/>
-      <c r="J94" s="6"/>
+      <c r="J94" s="62"/>
       <c r="K94" s="6"/>
-      <c r="M94" s="6"/>
-    </row>
-    <row r="95" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L94" s="6"/>
+      <c r="N94" s="6"/>
+    </row>
+    <row r="95" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6"/>
       <c r="F95" s="38"/>
-      <c r="J95" s="6"/>
+      <c r="J95" s="62"/>
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
-    </row>
-    <row r="96" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N95" s="6"/>
+    </row>
+    <row r="96" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6"/>
       <c r="F96" s="6"/>
-      <c r="J96" s="6"/>
+      <c r="J96" s="62"/>
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
-    </row>
-    <row r="97" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N96" s="6"/>
+    </row>
+    <row r="97" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6"/>
       <c r="F97" s="6"/>
-      <c r="J97" s="6"/>
+      <c r="J97" s="62"/>
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
-    </row>
-    <row r="98" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N97" s="6"/>
+    </row>
+    <row r="98" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6"/>
       <c r="F98" s="6"/>
-      <c r="J98" s="6"/>
+      <c r="J98" s="62"/>
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
-    </row>
-    <row r="99" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N98" s="6"/>
+    </row>
+    <row r="99" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6"/>
       <c r="F99" s="6"/>
-      <c r="J99" s="6"/>
+      <c r="J99" s="62"/>
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
-    </row>
-    <row r="100" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N99" s="6"/>
+    </row>
+    <row r="100" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6"/>
       <c r="F100" s="6"/>
-      <c r="J100" s="6"/>
+      <c r="J100" s="62"/>
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
-    </row>
-    <row r="101" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N100" s="6"/>
+    </row>
+    <row r="101" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6"/>
       <c r="F101" s="6"/>
-      <c r="J101" s="6"/>
+      <c r="J101" s="62"/>
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
-    </row>
-    <row r="102" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N101" s="6"/>
+    </row>
+    <row r="102" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6"/>
       <c r="F102" s="6"/>
-      <c r="J102" s="6"/>
+      <c r="J102" s="62"/>
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
       <c r="M102" s="6"/>
-    </row>
-    <row r="103" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N102" s="6"/>
+    </row>
+    <row r="103" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6"/>
       <c r="F103" s="33"/>
-      <c r="J103" s="6"/>
+      <c r="J103" s="62"/>
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
       <c r="M103" s="6"/>
-    </row>
-    <row r="104" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N103" s="6"/>
+    </row>
+    <row r="104" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6"/>
       <c r="F104" s="8"/>
-      <c r="J104" s="6"/>
+      <c r="J104" s="62"/>
       <c r="K104" s="6"/>
       <c r="L104" s="6"/>
       <c r="M104" s="6"/>
-    </row>
-    <row r="105" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N104" s="6"/>
+    </row>
+    <row r="105" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6"/>
       <c r="F105" s="8"/>
-      <c r="J105" s="6"/>
+      <c r="J105" s="62"/>
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
       <c r="M105" s="6"/>
-    </row>
-    <row r="106" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N105" s="6"/>
+    </row>
+    <row r="106" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6"/>
       <c r="F106" s="8"/>
-      <c r="J106" s="6"/>
+      <c r="J106" s="62"/>
       <c r="K106" s="6"/>
       <c r="L106" s="6"/>
       <c r="M106" s="6"/>
-    </row>
-    <row r="107" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N106" s="6"/>
+    </row>
+    <row r="107" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6"/>
       <c r="F107" s="8"/>
-      <c r="J107" s="6"/>
+      <c r="J107" s="62"/>
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
       <c r="M107" s="6"/>
-    </row>
-    <row r="108" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N107" s="6"/>
+    </row>
+    <row r="108" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6"/>
       <c r="F108" s="8"/>
-      <c r="J108" s="6"/>
+      <c r="J108" s="62"/>
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
-    </row>
-    <row r="109" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N108" s="6"/>
+    </row>
+    <row r="109" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6"/>
       <c r="F109" s="8"/>
-      <c r="J109" s="6"/>
+      <c r="J109" s="62"/>
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
-    </row>
-    <row r="110" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N109" s="6"/>
+    </row>
+    <row r="110" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6"/>
       <c r="F110" s="8"/>
-      <c r="J110" s="6"/>
+      <c r="J110" s="62"/>
       <c r="K110" s="6"/>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
-    </row>
-    <row r="111" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N110" s="6"/>
+    </row>
+    <row r="111" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6"/>
       <c r="F111" s="8"/>
-      <c r="J111" s="6"/>
+      <c r="J111" s="62"/>
       <c r="K111" s="6"/>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
-    </row>
-    <row r="112" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N111" s="6"/>
+    </row>
+    <row r="112" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6"/>
       <c r="F112" s="8"/>
-      <c r="J112" s="6"/>
+      <c r="J112" s="62"/>
       <c r="K112" s="6"/>
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
-    </row>
-    <row r="113" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N112" s="6"/>
+    </row>
+    <row r="113" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6"/>
       <c r="F113" s="8"/>
-      <c r="J113" s="6"/>
+      <c r="J113" s="62"/>
       <c r="K113" s="6"/>
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
-    </row>
-    <row r="114" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N113" s="6"/>
+    </row>
+    <row r="114" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6"/>
       <c r="F114" s="8"/>
-      <c r="J114" s="6"/>
+      <c r="J114" s="62"/>
       <c r="K114" s="6"/>
       <c r="L114" s="6"/>
       <c r="M114" s="6"/>
-    </row>
-    <row r="115" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N114" s="6"/>
+    </row>
+    <row r="115" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6"/>
       <c r="F115" s="8"/>
-      <c r="J115" s="6"/>
+      <c r="J115" s="62"/>
       <c r="K115" s="6"/>
       <c r="L115" s="6"/>
       <c r="M115" s="6"/>
-    </row>
-    <row r="116" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N115" s="6"/>
+    </row>
+    <row r="116" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6"/>
       <c r="F116" s="8"/>
-      <c r="J116" s="6"/>
+      <c r="J116" s="62"/>
       <c r="K116" s="6"/>
       <c r="L116" s="6"/>
       <c r="M116" s="6"/>
-    </row>
-    <row r="117" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N116" s="6"/>
+    </row>
+    <row r="117" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6"/>
       <c r="F117" s="8"/>
-      <c r="J117" s="6"/>
+      <c r="J117" s="62"/>
       <c r="K117" s="6"/>
       <c r="L117" s="6"/>
       <c r="M117" s="6"/>
-    </row>
-    <row r="118" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N117" s="6"/>
+    </row>
+    <row r="118" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6"/>
       <c r="F118" s="8"/>
-      <c r="J118" s="6"/>
+      <c r="J118" s="62"/>
       <c r="K118" s="6"/>
       <c r="L118" s="6"/>
       <c r="M118" s="6"/>
-    </row>
-    <row r="119" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N118" s="6"/>
+    </row>
+    <row r="119" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6"/>
       <c r="F119" s="8"/>
-      <c r="J119" s="6"/>
+      <c r="J119" s="62"/>
       <c r="K119" s="6"/>
       <c r="L119" s="6"/>
       <c r="M119" s="6"/>
-    </row>
-    <row r="120" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N119" s="6"/>
+    </row>
+    <row r="120" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6"/>
       <c r="F120" s="8"/>
-      <c r="J120" s="6"/>
+      <c r="J120" s="62"/>
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
       <c r="M120" s="6"/>
-    </row>
-    <row r="121" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N120" s="6"/>
+    </row>
+    <row r="121" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6"/>
       <c r="F121" s="8"/>
-      <c r="J121" s="6"/>
+      <c r="J121" s="62"/>
       <c r="K121" s="6"/>
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
-    </row>
-    <row r="122" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N121" s="6"/>
+    </row>
+    <row r="122" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6"/>
       <c r="F122" s="8"/>
-      <c r="J122" s="6"/>
+      <c r="J122" s="62"/>
       <c r="K122" s="6"/>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
-    </row>
-    <row r="123" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N122" s="6"/>
+    </row>
+    <row r="123" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6"/>
       <c r="F123" s="8"/>
-      <c r="J123" s="6"/>
+      <c r="J123" s="62"/>
       <c r="K123" s="6"/>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
-    </row>
-    <row r="124" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N123" s="6"/>
+    </row>
+    <row r="124" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6"/>
       <c r="F124" s="8"/>
-      <c r="J124" s="6"/>
+      <c r="J124" s="62"/>
       <c r="K124" s="6"/>
       <c r="L124" s="6"/>
       <c r="M124" s="6"/>
-    </row>
-    <row r="125" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N124" s="6"/>
+    </row>
+    <row r="125" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6"/>
       <c r="F125" s="8"/>
-      <c r="J125" s="6"/>
+      <c r="J125" s="62"/>
       <c r="K125" s="6"/>
       <c r="L125" s="6"/>
       <c r="M125" s="6"/>
-    </row>
-    <row r="126" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N125" s="6"/>
+    </row>
+    <row r="126" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6"/>
       <c r="F126" s="8"/>
-      <c r="J126" s="6"/>
+      <c r="J126" s="62"/>
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
-    </row>
-    <row r="127" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N126" s="6"/>
+    </row>
+    <row r="127" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6"/>
       <c r="F127" s="8"/>
-      <c r="J127" s="6"/>
+      <c r="J127" s="62"/>
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
       <c r="M127" s="6"/>
-    </row>
-    <row r="128" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N127" s="6"/>
+    </row>
+    <row r="128" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6"/>
       <c r="F128" s="8"/>
-      <c r="J128" s="6"/>
+      <c r="J128" s="62"/>
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
       <c r="M128" s="6"/>
-    </row>
-    <row r="129" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N128" s="6"/>
+    </row>
+    <row r="129" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6"/>
       <c r="F129" s="8"/>
-      <c r="J129" s="6"/>
+      <c r="J129" s="62"/>
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
       <c r="M129" s="6"/>
-    </row>
-    <row r="130" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N129" s="6"/>
+    </row>
+    <row r="130" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="6"/>
       <c r="F130" s="8"/>
-      <c r="J130" s="6"/>
+      <c r="J130" s="62"/>
       <c r="K130" s="6"/>
       <c r="L130" s="6"/>
       <c r="M130" s="6"/>
-    </row>
-    <row r="131" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N130" s="6"/>
+    </row>
+    <row r="131" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6"/>
       <c r="F131" s="8"/>
-      <c r="J131" s="6"/>
+      <c r="J131" s="62"/>
       <c r="K131" s="6"/>
       <c r="L131" s="6"/>
       <c r="M131" s="6"/>
-    </row>
-    <row r="132" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N131" s="6"/>
+    </row>
+    <row r="132" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="6"/>
       <c r="F132" s="8"/>
-      <c r="J132" s="6"/>
+      <c r="J132" s="62"/>
       <c r="K132" s="6"/>
       <c r="L132" s="6"/>
       <c r="M132" s="6"/>
-    </row>
-    <row r="133" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N132" s="6"/>
+    </row>
+    <row r="133" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6"/>
       <c r="F133" s="8"/>
-      <c r="J133" s="6"/>
+      <c r="J133" s="62"/>
       <c r="K133" s="6"/>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
-    </row>
-    <row r="134" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N133" s="6"/>
+    </row>
+    <row r="134" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="6"/>
       <c r="F134" s="8"/>
-      <c r="J134" s="6"/>
+      <c r="J134" s="62"/>
       <c r="K134" s="6"/>
       <c r="L134" s="6"/>
       <c r="M134" s="6"/>
-    </row>
-    <row r="135" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N134" s="6"/>
+    </row>
+    <row r="135" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6"/>
       <c r="F135" s="8"/>
-      <c r="J135" s="6"/>
+      <c r="J135" s="62"/>
       <c r="K135" s="6"/>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
-    </row>
-    <row r="136" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N135" s="6"/>
+    </row>
+    <row r="136" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="6"/>
       <c r="F136" s="8"/>
-      <c r="J136" s="6"/>
+      <c r="J136" s="62"/>
       <c r="K136" s="6"/>
       <c r="L136" s="6"/>
       <c r="M136" s="6"/>
-    </row>
-    <row r="137" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N136" s="6"/>
+    </row>
+    <row r="137" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6"/>
       <c r="F137" s="8"/>
-      <c r="J137" s="6"/>
+      <c r="J137" s="62"/>
       <c r="K137" s="6"/>
       <c r="L137" s="6"/>
       <c r="M137" s="6"/>
-    </row>
-    <row r="138" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N137" s="6"/>
+    </row>
+    <row r="138" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="6"/>
       <c r="F138" s="8"/>
-      <c r="J138" s="6"/>
+      <c r="J138" s="62"/>
       <c r="K138" s="6"/>
       <c r="L138" s="6"/>
       <c r="M138" s="6"/>
-    </row>
-    <row r="139" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N138" s="6"/>
+    </row>
+    <row r="139" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6"/>
       <c r="F139" s="8"/>
-      <c r="J139" s="6"/>
+      <c r="J139" s="62"/>
       <c r="K139" s="6"/>
       <c r="L139" s="6"/>
       <c r="M139" s="6"/>
-    </row>
-    <row r="140" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N139" s="6"/>
+    </row>
+    <row r="140" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="6"/>
       <c r="F140" s="8"/>
-      <c r="J140" s="6"/>
+      <c r="J140" s="62"/>
       <c r="K140" s="6"/>
       <c r="L140" s="6"/>
       <c r="M140" s="6"/>
-    </row>
-    <row r="141" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N140" s="6"/>
+    </row>
+    <row r="141" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6"/>
       <c r="F141" s="8"/>
-      <c r="J141" s="6"/>
+      <c r="J141" s="62"/>
       <c r="K141" s="6"/>
       <c r="L141" s="6"/>
       <c r="M141" s="6"/>
-    </row>
-    <row r="142" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N141" s="6"/>
+    </row>
+    <row r="142" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="6"/>
       <c r="F142" s="8"/>
-      <c r="J142" s="6"/>
+      <c r="J142" s="62"/>
       <c r="K142" s="6"/>
       <c r="L142" s="6"/>
       <c r="M142" s="6"/>
-    </row>
-    <row r="143" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N142" s="6"/>
+    </row>
+    <row r="143" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6"/>
       <c r="F143" s="8"/>
-      <c r="J143" s="6"/>
+      <c r="J143" s="62"/>
       <c r="K143" s="6"/>
       <c r="L143" s="6"/>
       <c r="M143" s="6"/>
-    </row>
-    <row r="144" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N143" s="6"/>
+    </row>
+    <row r="144" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="6"/>
       <c r="F144" s="8"/>
-      <c r="J144" s="6"/>
+      <c r="J144" s="62"/>
       <c r="K144" s="6"/>
       <c r="L144" s="6"/>
       <c r="M144" s="6"/>
-    </row>
-    <row r="145" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N144" s="6"/>
+    </row>
+    <row r="145" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6"/>
       <c r="F145" s="8"/>
-      <c r="J145" s="6"/>
+      <c r="J145" s="62"/>
       <c r="K145" s="6"/>
       <c r="L145" s="6"/>
       <c r="M145" s="6"/>
-    </row>
-    <row r="146" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N145" s="6"/>
+    </row>
+    <row r="146" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="6"/>
       <c r="F146" s="8"/>
-      <c r="J146" s="6"/>
+      <c r="J146" s="62"/>
       <c r="K146" s="6"/>
       <c r="L146" s="6"/>
       <c r="M146" s="6"/>
-    </row>
-    <row r="147" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N146" s="6"/>
+    </row>
+    <row r="147" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6"/>
       <c r="F147" s="8"/>
-      <c r="J147" s="6"/>
+      <c r="J147" s="62"/>
       <c r="K147" s="6"/>
       <c r="L147" s="6"/>
       <c r="M147" s="6"/>
-    </row>
-    <row r="148" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N147" s="6"/>
+    </row>
+    <row r="148" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="6"/>
       <c r="F148" s="8"/>
-      <c r="J148" s="6"/>
+      <c r="J148" s="62"/>
       <c r="K148" s="6"/>
       <c r="L148" s="6"/>
       <c r="M148" s="6"/>
-    </row>
-    <row r="149" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N148" s="6"/>
+    </row>
+    <row r="149" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6"/>
       <c r="F149" s="8"/>
-      <c r="J149" s="6"/>
+      <c r="J149" s="62"/>
       <c r="K149" s="6"/>
       <c r="L149" s="6"/>
       <c r="M149" s="6"/>
-    </row>
-    <row r="150" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N149" s="6"/>
+    </row>
+    <row r="150" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="6"/>
       <c r="F150" s="8"/>
-      <c r="J150" s="6"/>
+      <c r="J150" s="62"/>
       <c r="K150" s="6"/>
       <c r="L150" s="6"/>
       <c r="M150" s="6"/>
-    </row>
-    <row r="151" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N150" s="6"/>
+    </row>
+    <row r="151" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6"/>
       <c r="F151" s="8"/>
-      <c r="J151" s="6"/>
+      <c r="J151" s="62"/>
       <c r="K151" s="6"/>
       <c r="L151" s="6"/>
       <c r="M151" s="6"/>
-    </row>
-    <row r="152" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N151" s="6"/>
+    </row>
+    <row r="152" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="6"/>
       <c r="F152" s="8"/>
-      <c r="J152" s="6"/>
+      <c r="J152" s="62"/>
       <c r="K152" s="6"/>
       <c r="L152" s="6"/>
       <c r="M152" s="6"/>
-    </row>
-    <row r="153" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N152" s="6"/>
+    </row>
+    <row r="153" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6"/>
       <c r="F153" s="8"/>
-      <c r="J153" s="6"/>
+      <c r="J153" s="62"/>
       <c r="K153" s="6"/>
       <c r="L153" s="6"/>
       <c r="M153" s="6"/>
-    </row>
-    <row r="154" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N153" s="6"/>
+    </row>
+    <row r="154" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="6"/>
       <c r="F154" s="8"/>
-      <c r="J154" s="6"/>
+      <c r="J154" s="62"/>
       <c r="K154" s="6"/>
       <c r="L154" s="6"/>
       <c r="M154" s="6"/>
-    </row>
-    <row r="155" spans="1:13" ht="14" x14ac:dyDescent="0.3">
+      <c r="N154" s="6"/>
+    </row>
+    <row r="155" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A155" s="6"/>
       <c r="F155" s="8"/>
-      <c r="J155" s="6"/>
+      <c r="J155" s="62"/>
       <c r="K155" s="6"/>
       <c r="L155" s="6"/>
       <c r="M155" s="6"/>
-    </row>
-    <row r="156" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N155" s="6"/>
+    </row>
+    <row r="156" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="6"/>
       <c r="F156" s="8"/>
-      <c r="J156" s="6"/>
+      <c r="J156" s="62"/>
       <c r="K156" s="6"/>
       <c r="L156" s="6"/>
       <c r="M156" s="6"/>
-    </row>
-    <row r="157" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N156" s="6"/>
+    </row>
+    <row r="157" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6"/>
       <c r="F157" s="8"/>
-      <c r="J157" s="6"/>
+      <c r="J157" s="62"/>
       <c r="K157" s="6"/>
       <c r="L157" s="6"/>
       <c r="M157" s="6"/>
-    </row>
-    <row r="158" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N157" s="6"/>
+    </row>
+    <row r="158" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="6"/>
       <c r="F158" s="8"/>
-      <c r="J158" s="6"/>
+      <c r="J158" s="62"/>
       <c r="K158" s="6"/>
       <c r="L158" s="6"/>
       <c r="M158" s="6"/>
-    </row>
-    <row r="159" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N158" s="6"/>
+    </row>
+    <row r="159" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="6"/>
       <c r="F159" s="8"/>
-      <c r="J159" s="6"/>
+      <c r="J159" s="62"/>
       <c r="K159" s="6"/>
       <c r="L159" s="6"/>
       <c r="M159" s="6"/>
-    </row>
-    <row r="160" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N159" s="6"/>
+    </row>
+    <row r="160" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="6"/>
       <c r="F160" s="8"/>
-      <c r="J160" s="6"/>
+      <c r="J160" s="62"/>
       <c r="K160" s="6"/>
       <c r="L160" s="6"/>
       <c r="M160" s="6"/>
-    </row>
-    <row r="161" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N160" s="6"/>
+    </row>
+    <row r="161" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6"/>
       <c r="F161" s="8"/>
-      <c r="J161" s="6"/>
+      <c r="J161" s="62"/>
       <c r="K161" s="6"/>
       <c r="L161" s="6"/>
       <c r="M161" s="6"/>
-    </row>
-    <row r="162" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N161" s="6"/>
+    </row>
+    <row r="162" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="6"/>
       <c r="F162" s="8"/>
-      <c r="J162" s="6"/>
+      <c r="J162" s="62"/>
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
       <c r="M162" s="6"/>
-    </row>
-    <row r="163" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N162" s="6"/>
+    </row>
+    <row r="163" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="6"/>
       <c r="F163" s="8"/>
-      <c r="J163" s="6"/>
+      <c r="J163" s="62"/>
       <c r="K163" s="6"/>
       <c r="L163" s="6"/>
       <c r="M163" s="6"/>
-    </row>
-    <row r="164" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N163" s="6"/>
+    </row>
+    <row r="164" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="6"/>
       <c r="F164" s="8"/>
-      <c r="J164" s="6"/>
+      <c r="J164" s="62"/>
       <c r="K164" s="6"/>
       <c r="L164" s="6"/>
       <c r="M164" s="6"/>
-    </row>
-    <row r="165" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N164" s="6"/>
+    </row>
+    <row r="165" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6"/>
       <c r="F165" s="8"/>
-      <c r="J165" s="6"/>
+      <c r="J165" s="62"/>
       <c r="K165" s="6"/>
       <c r="L165" s="6"/>
       <c r="M165" s="6"/>
-    </row>
-    <row r="166" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N165" s="6"/>
+    </row>
+    <row r="166" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="6"/>
       <c r="F166" s="8"/>
-      <c r="J166" s="6"/>
+      <c r="J166" s="62"/>
       <c r="K166" s="6"/>
       <c r="L166" s="6"/>
       <c r="M166" s="6"/>
-    </row>
-    <row r="167" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N166" s="6"/>
+    </row>
+    <row r="167" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="6"/>
       <c r="F167" s="8"/>
-      <c r="J167" s="6"/>
+      <c r="J167" s="62"/>
       <c r="K167" s="6"/>
       <c r="L167" s="6"/>
       <c r="M167" s="6"/>
-    </row>
-    <row r="168" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N167" s="6"/>
+    </row>
+    <row r="168" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="6"/>
       <c r="F168" s="8"/>
-      <c r="J168" s="6"/>
+      <c r="J168" s="62"/>
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
       <c r="M168" s="6"/>
-    </row>
-    <row r="169" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N168" s="6"/>
+    </row>
+    <row r="169" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6"/>
       <c r="F169" s="8"/>
-      <c r="J169" s="6"/>
+      <c r="J169" s="62"/>
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
       <c r="M169" s="6"/>
-    </row>
-    <row r="170" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N169" s="6"/>
+    </row>
+    <row r="170" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="6"/>
       <c r="F170" s="8"/>
-      <c r="J170" s="6"/>
+      <c r="J170" s="62"/>
       <c r="K170" s="6"/>
       <c r="L170" s="6"/>
       <c r="M170" s="6"/>
-    </row>
-    <row r="171" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N170" s="6"/>
+    </row>
+    <row r="171" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6"/>
       <c r="F171" s="8"/>
-      <c r="J171" s="6"/>
+      <c r="J171" s="62"/>
       <c r="K171" s="6"/>
       <c r="L171" s="6"/>
       <c r="M171" s="6"/>
-    </row>
-    <row r="172" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N171" s="6"/>
+    </row>
+    <row r="172" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="6"/>
       <c r="F172" s="8"/>
-      <c r="J172" s="6"/>
+      <c r="J172" s="62"/>
       <c r="K172" s="6"/>
       <c r="L172" s="6"/>
       <c r="M172" s="6"/>
-    </row>
-    <row r="173" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N172" s="6"/>
+    </row>
+    <row r="173" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6"/>
       <c r="F173" s="8"/>
-      <c r="J173" s="6"/>
+      <c r="J173" s="62"/>
       <c r="K173" s="6"/>
       <c r="L173" s="6"/>
       <c r="M173" s="6"/>
-    </row>
-    <row r="174" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N173" s="6"/>
+    </row>
+    <row r="174" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="6"/>
       <c r="F174" s="8"/>
-      <c r="J174" s="6"/>
+      <c r="J174" s="62"/>
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
       <c r="M174" s="6"/>
-    </row>
-    <row r="175" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N174" s="6"/>
+    </row>
+    <row r="175" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6"/>
       <c r="F175" s="8"/>
-      <c r="J175" s="6"/>
+      <c r="J175" s="62"/>
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
       <c r="M175" s="6"/>
-    </row>
-    <row r="176" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N175" s="6"/>
+    </row>
+    <row r="176" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="6"/>
       <c r="F176" s="8"/>
-      <c r="J176" s="6"/>
+      <c r="J176" s="62"/>
       <c r="K176" s="6"/>
       <c r="L176" s="6"/>
       <c r="M176" s="6"/>
-    </row>
-    <row r="177" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N176" s="6"/>
+    </row>
+    <row r="177" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6"/>
       <c r="F177" s="8"/>
-      <c r="J177" s="6"/>
+      <c r="J177" s="62"/>
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
       <c r="M177" s="6"/>
-    </row>
-    <row r="178" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N177" s="6"/>
+    </row>
+    <row r="178" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="6"/>
       <c r="F178" s="8"/>
-      <c r="J178" s="6"/>
+      <c r="J178" s="62"/>
       <c r="K178" s="6"/>
       <c r="L178" s="6"/>
       <c r="M178" s="6"/>
-    </row>
-    <row r="179" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N178" s="6"/>
+    </row>
+    <row r="179" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6"/>
       <c r="F179" s="8"/>
-      <c r="J179" s="6"/>
+      <c r="J179" s="62"/>
       <c r="K179" s="6"/>
       <c r="L179" s="6"/>
       <c r="M179" s="6"/>
-    </row>
-    <row r="180" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N179" s="6"/>
+    </row>
+    <row r="180" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="6"/>
-      <c r="J180" s="6"/>
+      <c r="J180" s="62"/>
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
       <c r="M180" s="6"/>
-    </row>
-    <row r="181" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N180" s="6"/>
+    </row>
+    <row r="181" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6"/>
-      <c r="J181" s="6"/>
+      <c r="J181" s="62"/>
       <c r="K181" s="6"/>
       <c r="L181" s="6"/>
       <c r="M181" s="6"/>
-    </row>
-    <row r="182" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N181" s="6"/>
+    </row>
+    <row r="182" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="6"/>
-      <c r="J182" s="6"/>
+      <c r="J182" s="62"/>
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
       <c r="M182" s="6"/>
-    </row>
-    <row r="183" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N182" s="6"/>
+    </row>
+    <row r="183" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6"/>
-      <c r="J183" s="6"/>
+      <c r="J183" s="62"/>
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
       <c r="M183" s="6"/>
-    </row>
-    <row r="184" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N183" s="6"/>
+    </row>
+    <row r="184" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="6"/>
-      <c r="J184" s="6"/>
+      <c r="J184" s="62"/>
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
       <c r="M184" s="6"/>
-    </row>
-    <row r="185" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N184" s="6"/>
+    </row>
+    <row r="185" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="6"/>
-      <c r="J185" s="6"/>
+      <c r="J185" s="62"/>
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
-    </row>
-    <row r="186" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N185" s="6"/>
+    </row>
+    <row r="186" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="6"/>
-      <c r="J186" s="6"/>
+      <c r="J186" s="62"/>
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
       <c r="M186" s="6"/>
-    </row>
-    <row r="187" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N186" s="6"/>
+    </row>
+    <row r="187" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="6"/>
-      <c r="J187" s="6"/>
+      <c r="J187" s="62"/>
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
       <c r="M187" s="6"/>
-    </row>
-    <row r="188" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N187" s="6"/>
+    </row>
+    <row r="188" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="6"/>
-      <c r="J188" s="6"/>
+      <c r="J188" s="62"/>
       <c r="K188" s="6"/>
       <c r="L188" s="6"/>
       <c r="M188" s="6"/>
-    </row>
-    <row r="189" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N188" s="6"/>
+    </row>
+    <row r="189" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="6"/>
-      <c r="J189" s="6"/>
+      <c r="J189" s="62"/>
       <c r="K189" s="6"/>
       <c r="L189" s="6"/>
       <c r="M189" s="6"/>
-    </row>
-    <row r="190" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N189" s="6"/>
+    </row>
+    <row r="190" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="6"/>
-      <c r="J190" s="6"/>
+      <c r="J190" s="62"/>
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
       <c r="M190" s="6"/>
-    </row>
-    <row r="191" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N190" s="6"/>
+    </row>
+    <row r="191" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6"/>
-      <c r="J191" s="6"/>
+      <c r="J191" s="62"/>
       <c r="K191" s="6"/>
       <c r="L191" s="6"/>
       <c r="M191" s="6"/>
-    </row>
-    <row r="192" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N191" s="6"/>
+    </row>
+    <row r="192" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="6"/>
-      <c r="J192" s="6"/>
+      <c r="J192" s="62"/>
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
       <c r="M192" s="6"/>
-    </row>
-    <row r="193" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N192" s="6"/>
+    </row>
+    <row r="193" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6"/>
-      <c r="J193" s="6"/>
+      <c r="J193" s="62"/>
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
       <c r="M193" s="6"/>
-    </row>
-    <row r="194" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N193" s="6"/>
+    </row>
+    <row r="194" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="6"/>
-      <c r="J194" s="6"/>
+      <c r="J194" s="62"/>
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
       <c r="M194" s="6"/>
-    </row>
-    <row r="195" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N194" s="6"/>
+    </row>
+    <row r="195" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="6"/>
-      <c r="J195" s="6"/>
+      <c r="J195" s="62"/>
       <c r="K195" s="6"/>
       <c r="L195" s="6"/>
       <c r="M195" s="6"/>
-    </row>
-    <row r="196" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N195" s="6"/>
+    </row>
+    <row r="196" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="6"/>
-      <c r="J196" s="6"/>
+      <c r="J196" s="62"/>
       <c r="K196" s="6"/>
       <c r="L196" s="6"/>
       <c r="M196" s="6"/>
-    </row>
-    <row r="197" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N196" s="6"/>
+    </row>
+    <row r="197" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="6"/>
-      <c r="J197" s="6"/>
+      <c r="J197" s="62"/>
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
       <c r="M197" s="6"/>
-    </row>
-    <row r="198" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N197" s="6"/>
+    </row>
+    <row r="198" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="6"/>
-      <c r="J198" s="6"/>
+      <c r="J198" s="62"/>
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
       <c r="M198" s="6"/>
-    </row>
-    <row r="199" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N198" s="6"/>
+    </row>
+    <row r="199" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6"/>
-      <c r="J199" s="6"/>
+      <c r="J199" s="62"/>
       <c r="K199" s="6"/>
       <c r="L199" s="6"/>
       <c r="M199" s="6"/>
-    </row>
-    <row r="200" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N199" s="6"/>
+    </row>
+    <row r="200" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="6"/>
-      <c r="J200" s="6"/>
+      <c r="J200" s="62"/>
       <c r="K200" s="6"/>
       <c r="L200" s="6"/>
       <c r="M200" s="6"/>
-    </row>
-    <row r="201" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J201" s="6"/>
+      <c r="N200" s="6"/>
+    </row>
+    <row r="201" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K201" s="6"/>
-    </row>
-    <row r="202" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J202" s="6"/>
+      <c r="L201" s="6"/>
+    </row>
+    <row r="202" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K202" s="6"/>
-    </row>
-    <row r="203" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J203" s="6"/>
+      <c r="L202" s="6"/>
+    </row>
+    <row r="203" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K203" s="6"/>
-    </row>
-    <row r="204" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J204" s="6"/>
+      <c r="L203" s="6"/>
+    </row>
+    <row r="204" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K204" s="6"/>
-    </row>
-    <row r="205" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J205" s="6"/>
+      <c r="L204" s="6"/>
+    </row>
+    <row r="205" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K205" s="6"/>
+      <c r="L205" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9VerMhyw8tkGVsigbRsFbgV98qVp8TKcGSKGOI6rCRAlBliPKUvQMLRYg7Fek6Q9q3DpAfClI1nGwpU+Y1+tog==" saltValue="ptbYpMwFXuRBNByPq5lKYw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
-  <autoFilter ref="A1:Q28" xr:uid="{769FA850-14D9-4FA2-A099-BA408AF52616}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:Q41">
+  <sheetProtection algorithmName="SHA-512" hashValue="h4FRXlrvWDtCWqdjeG6EaCv6uIoAb/Xw0H663eE6nvD04dk9gBH5nE5PxEJ7s41mkjTYmNfX1ATKhXxoliRb7g==" saltValue="q5t6tiuZIaEmUW/tQVHy8g==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <autoFilter ref="A1:R28" xr:uid="{769FA850-14D9-4FA2-A099-BA408AF52616}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:R41">
     <sortCondition ref="A3:A41"/>
     <sortCondition ref="C3:C41"/>
     <sortCondition ref="B3:B41"/>
   </sortState>
-  <conditionalFormatting sqref="J1">
-    <cfRule type="containsBlanks" dxfId="8" priority="1">
-      <formula>LEN(TRIM(J1))=0</formula>
+  <conditionalFormatting sqref="K1">
+    <cfRule type="containsBlanks" dxfId="9" priority="2">
+      <formula>LEN(TRIM(K1))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="Nein">
-      <formula>NOT(ISERROR(SEARCH("Nein",J1)))</formula>
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="Nein">
+      <formula>NOT(ISERROR(SEARCH("Nein",K1)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>"Nein"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J2">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>ISBLANK(J2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2" xr:uid="{2AD60BF0-74CD-4499-BE9F-7ADF73016574}">
+      <formula1>"Ja, Nein"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
@@ -3651,25 +3875,25 @@
           <x14:formula1>
             <xm:f>'Drop Down'!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>L4:L93 L95:L200</xm:sqref>
+          <xm:sqref>M4:M93 M95:M200</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7D46E36D-4921-4414-BB8C-91C525BAA0A2}">
           <x14:formula1>
             <xm:f>'Drop Down'!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>J4:J201</xm:sqref>
+          <xm:sqref>K4:K201</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D00EFC96-80A8-4FC6-9F6F-2F17BC12BD76}">
           <x14:formula1>
             <xm:f>'Drop Down'!$G$2:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>K4:K200</xm:sqref>
+          <xm:sqref>L4:L200</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B44B49D8-A31B-4FB0-B013-7B7FCCD759EB}">
           <x14:formula1>
             <xm:f>'Drop Down'!$H$2:$H$4</xm:f>
           </x14:formula1>
-          <xm:sqref>M3:M200</xm:sqref>
+          <xm:sqref>N3:N200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3680,29 +3904,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C46933-1A25-4AF2-9CC0-718F5FE19CAA}">
   <dimension ref="A1:DE277"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.08203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="26.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.625" style="1" customWidth="1"/>
     <col min="4" max="5" width="26" style="48" customWidth="1"/>
-    <col min="6" max="6" width="30.58203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="48.08203125" style="48" customWidth="1"/>
+    <col min="6" max="6" width="30.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="48.125" style="48" customWidth="1"/>
     <col min="8" max="8" width="64.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="92.58203125" style="48" customWidth="1"/>
-    <col min="10" max="10" width="31.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="92.625" style="48" customWidth="1"/>
+    <col min="10" max="10" width="31.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="25.75" style="1" customWidth="1"/>
     <col min="12" max="12" width="28" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.58203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="33.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="33.125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="22.25" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20.58203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="21.08203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.08203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="11.08203125" style="1"/>
+    <col min="16" max="16" width="20.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="21.125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="11.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:109" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:109" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3758,7 +3982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:109" s="46" customFormat="1" ht="168.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:109" s="46" customFormat="1" ht="210.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="44"/>
       <c r="B2" s="44" t="s">
         <v>4</v>
@@ -3766,13 +3990,13 @@
       <c r="C2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="49" t="s">
         <v>76</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="51" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="47" t="s">
@@ -3781,34 +4005,34 @@
       <c r="H2" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="52" t="s">
+      <c r="J2" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="52" t="s">
+      <c r="K2" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="52" t="s">
+      <c r="L2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="52" t="s">
+      <c r="M2" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="52" t="s">
+      <c r="N2" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="52" t="s">
+      <c r="O2" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="52" t="s">
+      <c r="P2" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="52" t="s">
+      <c r="Q2" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="52" t="s">
+      <c r="R2" s="49" t="s">
         <v>60</v>
       </c>
       <c r="S2" s="45"/>
@@ -3903,57 +4127,57 @@
       <c r="DD2" s="45"/>
       <c r="DE2" s="45"/>
     </row>
-    <row r="3" spans="1:109" s="56" customFormat="1" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:109" s="53" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="I3" s="53" t="s">
+      <c r="I3" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="J3" s="53" t="s">
+      <c r="J3" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="53" t="s">
+      <c r="K3" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="53" t="s">
+      <c r="L3" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="M3" s="53" t="s">
+      <c r="M3" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="N3" s="53" t="s">
+      <c r="N3" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="O3" s="53" t="s">
+      <c r="O3" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="57"/>
-    </row>
-    <row r="4" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P3" s="50"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="54"/>
+    </row>
+    <row r="4" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
@@ -3973,7 +4197,7 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="11"/>
       <c r="C5" s="14"/>
@@ -3992,7 +4216,7 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="11"/>
       <c r="C6" s="14"/>
@@ -4011,7 +4235,7 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="11"/>
       <c r="C7" s="14"/>
@@ -4031,7 +4255,7 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="11"/>
       <c r="C8" s="22"/>
@@ -4051,7 +4275,7 @@
       <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
     </row>
-    <row r="9" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="11"/>
       <c r="C9" s="14"/>
@@ -4070,7 +4294,7 @@
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
     </row>
-    <row r="10" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="11"/>
       <c r="C10" s="14"/>
@@ -4090,7 +4314,7 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="11"/>
       <c r="C11" s="14"/>
@@ -4110,7 +4334,7 @@
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
     </row>
-    <row r="12" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="11"/>
       <c r="C12" s="14"/>
@@ -4130,7 +4354,7 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="11"/>
       <c r="C13" s="14"/>
@@ -4150,7 +4374,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="11"/>
       <c r="C14" s="14"/>
@@ -4170,7 +4394,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="11"/>
       <c r="C15" s="14"/>
@@ -4190,7 +4414,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="11"/>
       <c r="C16" s="2"/>
@@ -4207,7 +4431,7 @@
       <c r="N16" s="6"/>
       <c r="O16" s="21"/>
     </row>
-    <row r="17" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="11"/>
       <c r="C17" s="14"/>
@@ -4227,7 +4451,7 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
     </row>
-    <row r="18" spans="1:20" s="9" customFormat="1" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="11"/>
       <c r="C18" s="23"/>
@@ -4248,7 +4472,7 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
     </row>
-    <row r="19" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="11"/>
       <c r="C19" s="21"/>
@@ -4265,7 +4489,7 @@
       <c r="N19" s="6"/>
       <c r="O19" s="9"/>
     </row>
-    <row r="20" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="11"/>
       <c r="C20" s="21"/>
@@ -4282,7 +4506,7 @@
       <c r="N20" s="6"/>
       <c r="O20" s="9"/>
     </row>
-    <row r="21" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="11"/>
       <c r="C21" s="14"/>
@@ -4298,7 +4522,7 @@
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="B22" s="11"/>
       <c r="C22" s="25"/>
@@ -4318,7 +4542,7 @@
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
     </row>
-    <row r="23" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="11"/>
       <c r="C23" s="21"/>
@@ -4339,7 +4563,7 @@
       <c r="S23" s="9"/>
       <c r="T23" s="9"/>
     </row>
-    <row r="24" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
       <c r="B24" s="11"/>
       <c r="C24" s="14"/>
@@ -4359,7 +4583,7 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
     </row>
-    <row r="25" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="B25" s="11"/>
       <c r="C25" s="14"/>
@@ -4376,7 +4600,7 @@
       <c r="N25" s="6"/>
       <c r="O25" s="9"/>
     </row>
-    <row r="26" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="11"/>
       <c r="C26" s="14"/>
@@ -4396,7 +4620,7 @@
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
     </row>
-    <row r="27" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="11"/>
       <c r="C27" s="14"/>
@@ -4415,7 +4639,7 @@
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
     </row>
-    <row r="28" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="B28" s="11"/>
       <c r="C28" s="14"/>
@@ -4431,7 +4655,7 @@
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="B29" s="11"/>
       <c r="C29" s="14"/>
@@ -4447,7 +4671,7 @@
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
-    <row r="30" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="B30" s="11"/>
       <c r="C30" s="14"/>
@@ -4465,7 +4689,7 @@
       <c r="S30" s="9"/>
       <c r="T30" s="9"/>
     </row>
-    <row r="31" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
       <c r="B31" s="11"/>
       <c r="C31" s="14"/>
@@ -4487,7 +4711,7 @@
       <c r="S31" s="9"/>
       <c r="T31" s="9"/>
     </row>
-    <row r="32" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
       <c r="B32" s="11"/>
       <c r="C32" s="14"/>
@@ -4509,7 +4733,7 @@
       <c r="S32" s="9"/>
       <c r="T32" s="9"/>
     </row>
-    <row r="33" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
       <c r="B33" s="11"/>
       <c r="C33" s="8"/>
@@ -4531,7 +4755,7 @@
       <c r="S33" s="9"/>
       <c r="T33" s="9"/>
     </row>
-    <row r="34" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
       <c r="B34" s="11"/>
       <c r="C34" s="14"/>
@@ -4548,7 +4772,7 @@
       <c r="N34" s="6"/>
       <c r="O34" s="9"/>
     </row>
-    <row r="35" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="B35" s="11"/>
       <c r="C35" s="14"/>
@@ -4565,7 +4789,7 @@
       <c r="N35" s="6"/>
       <c r="O35" s="9"/>
     </row>
-    <row r="36" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
       <c r="B36" s="11"/>
       <c r="C36" s="21"/>
@@ -4585,7 +4809,7 @@
       <c r="Q36" s="21"/>
       <c r="R36" s="21"/>
     </row>
-    <row r="37" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
       <c r="B37" s="11"/>
       <c r="C37" s="14"/>
@@ -4605,7 +4829,7 @@
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
     </row>
-    <row r="38" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
       <c r="B38" s="11"/>
       <c r="C38" s="14"/>
@@ -4622,7 +4846,7 @@
       <c r="N38" s="6"/>
       <c r="O38" s="15"/>
     </row>
-    <row r="39" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="11"/>
       <c r="C39" s="14"/>
@@ -4638,7 +4862,7 @@
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6"/>
       <c r="B40" s="11"/>
       <c r="D40" s="48"/>
@@ -4654,7 +4878,7 @@
       <c r="N40" s="6"/>
       <c r="O40" s="21"/>
     </row>
-    <row r="41" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
       <c r="B41" s="11"/>
       <c r="C41" s="21"/>
@@ -4673,7 +4897,7 @@
       <c r="S41" s="2"/>
       <c r="T41" s="2"/>
     </row>
-    <row r="42" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
       <c r="B42" s="11"/>
       <c r="C42" s="29"/>
@@ -4690,7 +4914,7 @@
       <c r="N42" s="6"/>
       <c r="O42" s="21"/>
     </row>
-    <row r="43" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
       <c r="B43" s="11"/>
       <c r="D43" s="48"/>
@@ -4706,7 +4930,7 @@
       <c r="N43" s="6"/>
       <c r="O43" s="21"/>
     </row>
-    <row r="44" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
       <c r="B44" s="11"/>
       <c r="D44" s="48"/>
@@ -4722,7 +4946,7 @@
       <c r="N44" s="6"/>
       <c r="O44" s="15"/>
     </row>
-    <row r="45" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="B45" s="11"/>
       <c r="D45" s="48"/>
@@ -4738,7 +4962,7 @@
       <c r="N45" s="6"/>
       <c r="O45" s="12"/>
     </row>
-    <row r="46" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="B46" s="11"/>
       <c r="C46" s="8"/>
@@ -4760,7 +4984,7 @@
       <c r="S46" s="9"/>
       <c r="T46" s="9"/>
     </row>
-    <row r="47" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6"/>
       <c r="B47" s="11"/>
       <c r="C47" s="2"/>
@@ -4780,7 +5004,7 @@
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
     </row>
-    <row r="48" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
       <c r="B48" s="11"/>
       <c r="C48" s="14"/>
@@ -4798,7 +5022,7 @@
       <c r="Q48" s="12"/>
       <c r="R48" s="12"/>
     </row>
-    <row r="49" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
       <c r="B49" s="11"/>
       <c r="D49" s="48"/>
@@ -4816,7 +5040,7 @@
       <c r="Q49" s="21"/>
       <c r="R49" s="21"/>
     </row>
-    <row r="50" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="6"/>
       <c r="B50" s="11"/>
       <c r="C50" s="9"/>
@@ -4836,7 +5060,7 @@
       <c r="Q50" s="9"/>
       <c r="R50" s="9"/>
     </row>
-    <row r="51" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
       <c r="B51" s="11"/>
       <c r="D51" s="48"/>
@@ -4855,7 +5079,7 @@
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
     </row>
-    <row r="52" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6"/>
       <c r="B52" s="11"/>
       <c r="D52" s="48"/>
@@ -4872,7 +5096,7 @@
       <c r="O52" s="15"/>
       <c r="P52" s="9"/>
     </row>
-    <row r="53" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6"/>
       <c r="B53" s="11"/>
       <c r="C53" s="21"/>
@@ -4892,7 +5116,7 @@
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
     </row>
-    <row r="54" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
       <c r="B54" s="11"/>
       <c r="C54" s="14"/>
@@ -4911,7 +5135,7 @@
       <c r="Q54" s="33"/>
       <c r="R54" s="33"/>
     </row>
-    <row r="55" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
       <c r="B55" s="11"/>
       <c r="C55" s="14"/>
@@ -4927,7 +5151,7 @@
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6"/>
       <c r="B56" s="11"/>
       <c r="C56" s="14"/>
@@ -4943,7 +5167,7 @@
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
       <c r="B57" s="11"/>
       <c r="C57" s="14"/>
@@ -4959,7 +5183,7 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6"/>
       <c r="B58" s="11"/>
       <c r="C58" s="14"/>
@@ -4975,7 +5199,7 @@
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6"/>
       <c r="B59" s="11"/>
       <c r="C59" s="14"/>
@@ -4991,7 +5215,7 @@
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:20" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" s="35" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6"/>
       <c r="B60" s="11"/>
       <c r="C60" s="14"/>
@@ -5011,7 +5235,7 @@
       <c r="Q60" s="9"/>
       <c r="R60" s="9"/>
     </row>
-    <row r="61" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
       <c r="B61" s="11"/>
       <c r="C61" s="14"/>
@@ -5027,7 +5251,7 @@
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6"/>
       <c r="B62" s="11"/>
       <c r="C62" s="14"/>
@@ -5047,7 +5271,7 @@
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
     </row>
-    <row r="63" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6"/>
       <c r="B63" s="11"/>
       <c r="C63" s="14"/>
@@ -5065,7 +5289,7 @@
       <c r="Q63" s="21"/>
       <c r="R63" s="21"/>
     </row>
-    <row r="64" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6"/>
       <c r="B64" s="11"/>
       <c r="C64" s="14"/>
@@ -5083,7 +5307,7 @@
       <c r="Q64" s="21"/>
       <c r="R64" s="21"/>
     </row>
-    <row r="65" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6"/>
       <c r="B65" s="11"/>
       <c r="C65" s="14"/>
@@ -5101,7 +5325,7 @@
       <c r="Q65" s="21"/>
       <c r="R65" s="21"/>
     </row>
-    <row r="66" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="6"/>
       <c r="B66" s="11"/>
       <c r="C66" s="14"/>
@@ -5121,7 +5345,7 @@
       <c r="Q66" s="9"/>
       <c r="R66" s="9"/>
     </row>
-    <row r="67" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6"/>
       <c r="B67" s="11"/>
       <c r="C67" s="14"/>
@@ -5138,7 +5362,7 @@
       <c r="S67" s="9"/>
       <c r="T67" s="9"/>
     </row>
-    <row r="68" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
       <c r="B68" s="11"/>
       <c r="C68" s="14"/>
@@ -5157,7 +5381,7 @@
       <c r="Q68" s="9"/>
       <c r="R68" s="9"/>
     </row>
-    <row r="69" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6"/>
       <c r="B69" s="11"/>
       <c r="C69" s="14"/>
@@ -5172,7 +5396,7 @@
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
-    <row r="70" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6"/>
       <c r="B70" s="11"/>
       <c r="C70" s="14"/>
@@ -5189,7 +5413,7 @@
       <c r="S70" s="9"/>
       <c r="T70" s="9"/>
     </row>
-    <row r="71" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
       <c r="B71" s="11"/>
       <c r="C71" s="14"/>
@@ -5204,7 +5428,7 @@
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
-    <row r="72" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6"/>
       <c r="B72" s="11"/>
       <c r="C72" s="14"/>
@@ -5219,7 +5443,7 @@
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
-    <row r="73" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6"/>
       <c r="B73" s="11"/>
       <c r="C73" s="14"/>
@@ -5235,7 +5459,7 @@
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
-    <row r="74" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="6"/>
       <c r="B74" s="11"/>
       <c r="C74" s="14"/>
@@ -5255,7 +5479,7 @@
       <c r="S74" s="9"/>
       <c r="T74" s="9"/>
     </row>
-    <row r="75" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6"/>
       <c r="B75" s="11"/>
       <c r="C75" s="14"/>
@@ -5271,7 +5495,7 @@
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
-    <row r="76" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6"/>
       <c r="B76" s="11"/>
       <c r="C76" s="14"/>
@@ -5287,7 +5511,7 @@
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
       <c r="B77" s="11"/>
       <c r="C77" s="21"/>
@@ -5304,7 +5528,7 @@
       <c r="N77" s="6"/>
       <c r="O77" s="21"/>
     </row>
-    <row r="78" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6"/>
       <c r="B78" s="11"/>
       <c r="C78" s="14"/>
@@ -5323,7 +5547,7 @@
       <c r="S78" s="9"/>
       <c r="T78" s="9"/>
     </row>
-    <row r="79" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6"/>
       <c r="B79" s="11"/>
       <c r="C79" s="14"/>
@@ -5342,7 +5566,7 @@
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
     </row>
-    <row r="80" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6"/>
       <c r="B80" s="11"/>
       <c r="D80" s="48"/>
@@ -5357,7 +5581,7 @@
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
-    <row r="81" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6"/>
       <c r="B81" s="11"/>
       <c r="D81" s="48"/>
@@ -5376,7 +5600,7 @@
       <c r="Q81" s="21"/>
       <c r="R81" s="21"/>
     </row>
-    <row r="82" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6"/>
       <c r="B82" s="11"/>
       <c r="D82" s="48"/>
@@ -5395,7 +5619,7 @@
       <c r="Q82" s="21"/>
       <c r="R82" s="21"/>
     </row>
-    <row r="83" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6"/>
       <c r="B83" s="11"/>
       <c r="D83" s="48"/>
@@ -5414,7 +5638,7 @@
       <c r="S83" s="2"/>
       <c r="T83" s="2"/>
     </row>
-    <row r="84" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6"/>
       <c r="B84" s="11"/>
       <c r="C84" s="9"/>
@@ -5431,7 +5655,7 @@
       <c r="N84" s="6"/>
       <c r="O84" s="9"/>
     </row>
-    <row r="85" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -5450,7 +5674,7 @@
       <c r="Q85" s="6"/>
       <c r="R85" s="6"/>
     </row>
-    <row r="86" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6"/>
       <c r="B86" s="11"/>
       <c r="C86" s="12"/>
@@ -5470,7 +5694,7 @@
       <c r="Q86" s="8"/>
       <c r="R86" s="8"/>
     </row>
-    <row r="87" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -5490,7 +5714,7 @@
       <c r="Q87" s="6"/>
       <c r="R87" s="6"/>
     </row>
-    <row r="88" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6"/>
       <c r="B88" s="11"/>
       <c r="C88" s="11"/>
@@ -5510,7 +5734,7 @@
       <c r="Q88" s="6"/>
       <c r="R88" s="11"/>
     </row>
-    <row r="89" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6"/>
       <c r="B89" s="11"/>
       <c r="C89" s="6"/>
@@ -5530,7 +5754,7 @@
       <c r="Q89" s="37"/>
       <c r="R89" s="21"/>
     </row>
-    <row r="90" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6"/>
       <c r="B90" s="11"/>
       <c r="C90" s="12"/>
@@ -5544,7 +5768,7 @@
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
-    <row r="91" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6"/>
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
@@ -5564,7 +5788,7 @@
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
     </row>
-    <row r="92" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -5584,7 +5808,7 @@
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
     </row>
-    <row r="93" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
@@ -5604,7 +5828,7 @@
       <c r="Q93" s="12"/>
       <c r="R93" s="12"/>
     </row>
-    <row r="94" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -5624,7 +5848,7 @@
       <c r="Q94" s="6"/>
       <c r="R94" s="21"/>
     </row>
-    <row r="95" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="38"/>
@@ -5644,7 +5868,7 @@
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
     </row>
-    <row r="96" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -5664,7 +5888,7 @@
       <c r="Q96" s="40"/>
       <c r="R96" s="40"/>
     </row>
-    <row r="97" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -5684,7 +5908,7 @@
       <c r="Q97" s="40"/>
       <c r="R97" s="40"/>
     </row>
-    <row r="98" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6"/>
       <c r="B98" s="11"/>
       <c r="C98" s="6"/>
@@ -5704,7 +5928,7 @@
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
     </row>
-    <row r="99" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6"/>
       <c r="B99" s="11"/>
       <c r="C99" s="6"/>
@@ -5724,7 +5948,7 @@
       <c r="Q99" s="15"/>
       <c r="R99" s="2"/>
     </row>
-    <row r="100" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6"/>
       <c r="B100" s="11"/>
       <c r="C100" s="6"/>
@@ -5744,7 +5968,7 @@
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
     </row>
-    <row r="101" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6"/>
       <c r="B101" s="11"/>
       <c r="C101" s="6"/>
@@ -5764,7 +5988,7 @@
       <c r="Q101" s="6"/>
       <c r="R101" s="6"/>
     </row>
-    <row r="102" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6"/>
       <c r="B102" s="11"/>
       <c r="C102" s="6"/>
@@ -5784,7 +6008,7 @@
       <c r="Q102" s="35"/>
       <c r="R102" s="35"/>
     </row>
-    <row r="103" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6"/>
       <c r="B103" s="11"/>
       <c r="C103" s="41"/>
@@ -5804,7 +6028,7 @@
       <c r="Q103" s="35"/>
       <c r="R103" s="35"/>
     </row>
-    <row r="104" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6"/>
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
@@ -5816,7 +6040,7 @@
       <c r="M104" s="6"/>
       <c r="N104" s="6"/>
     </row>
-    <row r="105" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6"/>
       <c r="D105" s="48"/>
       <c r="E105" s="48"/>
@@ -5828,7 +6052,7 @@
       <c r="M105" s="6"/>
       <c r="N105" s="6"/>
     </row>
-    <row r="106" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6"/>
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
@@ -5840,7 +6064,7 @@
       <c r="M106" s="6"/>
       <c r="N106" s="6"/>
     </row>
-    <row r="107" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6"/>
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
@@ -5852,7 +6076,7 @@
       <c r="M107" s="6"/>
       <c r="N107" s="6"/>
     </row>
-    <row r="108" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6"/>
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
@@ -5864,7 +6088,7 @@
       <c r="M108" s="6"/>
       <c r="N108" s="6"/>
     </row>
-    <row r="109" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6"/>
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
@@ -5876,7 +6100,7 @@
       <c r="M109" s="6"/>
       <c r="N109" s="6"/>
     </row>
-    <row r="110" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6"/>
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
@@ -5888,7 +6112,7 @@
       <c r="M110" s="6"/>
       <c r="N110" s="6"/>
     </row>
-    <row r="111" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6"/>
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
@@ -5900,7 +6124,7 @@
       <c r="M111" s="6"/>
       <c r="N111" s="6"/>
     </row>
-    <row r="112" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6"/>
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
@@ -5912,7 +6136,7 @@
       <c r="M112" s="6"/>
       <c r="N112" s="6"/>
     </row>
-    <row r="113" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
@@ -5924,7 +6148,7 @@
       <c r="M113" s="6"/>
       <c r="N113" s="6"/>
     </row>
-    <row r="114" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
@@ -5936,7 +6160,7 @@
       <c r="M114" s="6"/>
       <c r="N114" s="6"/>
     </row>
-    <row r="115" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
@@ -5948,7 +6172,7 @@
       <c r="M115" s="6"/>
       <c r="N115" s="6"/>
     </row>
-    <row r="116" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6"/>
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
@@ -5960,7 +6184,7 @@
       <c r="M116" s="6"/>
       <c r="N116" s="6"/>
     </row>
-    <row r="117" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
@@ -5972,7 +6196,7 @@
       <c r="M117" s="6"/>
       <c r="N117" s="6"/>
     </row>
-    <row r="118" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
@@ -5984,7 +6208,7 @@
       <c r="M118" s="6"/>
       <c r="N118" s="6"/>
     </row>
-    <row r="119" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
@@ -5996,7 +6220,7 @@
       <c r="M119" s="6"/>
       <c r="N119" s="6"/>
     </row>
-    <row r="120" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6"/>
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
@@ -6008,7 +6232,7 @@
       <c r="M120" s="6"/>
       <c r="N120" s="6"/>
     </row>
-    <row r="121" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
@@ -6020,7 +6244,7 @@
       <c r="M121" s="6"/>
       <c r="N121" s="6"/>
     </row>
-    <row r="122" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
@@ -6032,7 +6256,7 @@
       <c r="M122" s="6"/>
       <c r="N122" s="6"/>
     </row>
-    <row r="123" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
@@ -6044,7 +6268,7 @@
       <c r="M123" s="6"/>
       <c r="N123" s="6"/>
     </row>
-    <row r="124" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6"/>
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
@@ -6056,7 +6280,7 @@
       <c r="M124" s="6"/>
       <c r="N124" s="6"/>
     </row>
-    <row r="125" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
@@ -6068,7 +6292,7 @@
       <c r="M125" s="6"/>
       <c r="N125" s="6"/>
     </row>
-    <row r="126" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
@@ -6080,7 +6304,7 @@
       <c r="M126" s="6"/>
       <c r="N126" s="6"/>
     </row>
-    <row r="127" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6"/>
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
@@ -6092,7 +6316,7 @@
       <c r="M127" s="6"/>
       <c r="N127" s="6"/>
     </row>
-    <row r="128" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6"/>
       <c r="D128" s="48"/>
       <c r="E128" s="48"/>
@@ -6104,7 +6328,7 @@
       <c r="M128" s="6"/>
       <c r="N128" s="6"/>
     </row>
-    <row r="129" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6"/>
       <c r="D129" s="48"/>
       <c r="E129" s="48"/>
@@ -6116,7 +6340,7 @@
       <c r="M129" s="6"/>
       <c r="N129" s="6"/>
     </row>
-    <row r="130" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="6"/>
       <c r="D130" s="48"/>
       <c r="E130" s="48"/>
@@ -6128,7 +6352,7 @@
       <c r="M130" s="6"/>
       <c r="N130" s="6"/>
     </row>
-    <row r="131" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6"/>
       <c r="D131" s="48"/>
       <c r="E131" s="48"/>
@@ -6140,7 +6364,7 @@
       <c r="M131" s="6"/>
       <c r="N131" s="6"/>
     </row>
-    <row r="132" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="6"/>
       <c r="D132" s="48"/>
       <c r="E132" s="48"/>
@@ -6152,7 +6376,7 @@
       <c r="M132" s="6"/>
       <c r="N132" s="6"/>
     </row>
-    <row r="133" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6"/>
       <c r="D133" s="48"/>
       <c r="E133" s="48"/>
@@ -6164,7 +6388,7 @@
       <c r="M133" s="6"/>
       <c r="N133" s="6"/>
     </row>
-    <row r="134" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="6"/>
       <c r="D134" s="48"/>
       <c r="E134" s="48"/>
@@ -6176,7 +6400,7 @@
       <c r="M134" s="6"/>
       <c r="N134" s="6"/>
     </row>
-    <row r="135" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6"/>
       <c r="D135" s="48"/>
       <c r="E135" s="48"/>
@@ -6188,7 +6412,7 @@
       <c r="M135" s="6"/>
       <c r="N135" s="6"/>
     </row>
-    <row r="136" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="6"/>
       <c r="D136" s="48"/>
       <c r="E136" s="48"/>
@@ -6200,7 +6424,7 @@
       <c r="M136" s="6"/>
       <c r="N136" s="6"/>
     </row>
-    <row r="137" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6"/>
       <c r="D137" s="48"/>
       <c r="E137" s="48"/>
@@ -6212,7 +6436,7 @@
       <c r="M137" s="6"/>
       <c r="N137" s="6"/>
     </row>
-    <row r="138" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="6"/>
       <c r="D138" s="48"/>
       <c r="E138" s="48"/>
@@ -6224,7 +6448,7 @@
       <c r="M138" s="6"/>
       <c r="N138" s="6"/>
     </row>
-    <row r="139" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6"/>
       <c r="D139" s="48"/>
       <c r="E139" s="48"/>
@@ -6236,7 +6460,7 @@
       <c r="M139" s="6"/>
       <c r="N139" s="6"/>
     </row>
-    <row r="140" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="6"/>
       <c r="D140" s="48"/>
       <c r="E140" s="48"/>
@@ -6248,7 +6472,7 @@
       <c r="M140" s="6"/>
       <c r="N140" s="6"/>
     </row>
-    <row r="141" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6"/>
       <c r="D141" s="48"/>
       <c r="E141" s="48"/>
@@ -6260,7 +6484,7 @@
       <c r="M141" s="6"/>
       <c r="N141" s="6"/>
     </row>
-    <row r="142" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A142" s="6"/>
       <c r="D142" s="48"/>
       <c r="E142" s="48"/>
@@ -6272,7 +6496,7 @@
       <c r="M142" s="6"/>
       <c r="N142" s="6"/>
     </row>
-    <row r="143" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6"/>
       <c r="D143" s="48"/>
       <c r="E143" s="48"/>
@@ -6284,7 +6508,7 @@
       <c r="M143" s="6"/>
       <c r="N143" s="6"/>
     </row>
-    <row r="144" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A144" s="6"/>
       <c r="D144" s="48"/>
       <c r="E144" s="48"/>
@@ -6296,7 +6520,7 @@
       <c r="M144" s="6"/>
       <c r="N144" s="6"/>
     </row>
-    <row r="145" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6"/>
       <c r="D145" s="48"/>
       <c r="E145" s="48"/>
@@ -6308,7 +6532,7 @@
       <c r="M145" s="6"/>
       <c r="N145" s="6"/>
     </row>
-    <row r="146" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A146" s="6"/>
       <c r="D146" s="48"/>
       <c r="E146" s="48"/>
@@ -6320,7 +6544,7 @@
       <c r="M146" s="6"/>
       <c r="N146" s="6"/>
     </row>
-    <row r="147" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6"/>
       <c r="D147" s="48"/>
       <c r="E147" s="48"/>
@@ -6332,7 +6556,7 @@
       <c r="M147" s="6"/>
       <c r="N147" s="6"/>
     </row>
-    <row r="148" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A148" s="6"/>
       <c r="D148" s="48"/>
       <c r="E148" s="48"/>
@@ -6344,7 +6568,7 @@
       <c r="M148" s="6"/>
       <c r="N148" s="6"/>
     </row>
-    <row r="149" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6"/>
       <c r="D149" s="48"/>
       <c r="E149" s="48"/>
@@ -6356,7 +6580,7 @@
       <c r="M149" s="6"/>
       <c r="N149" s="6"/>
     </row>
-    <row r="150" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A150" s="6"/>
       <c r="D150" s="48"/>
       <c r="E150" s="48"/>
@@ -6368,7 +6592,7 @@
       <c r="M150" s="6"/>
       <c r="N150" s="6"/>
     </row>
-    <row r="151" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6"/>
       <c r="D151" s="48"/>
       <c r="E151" s="48"/>
@@ -6380,7 +6604,7 @@
       <c r="M151" s="6"/>
       <c r="N151" s="6"/>
     </row>
-    <row r="152" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A152" s="6"/>
       <c r="D152" s="48"/>
       <c r="E152" s="48"/>
@@ -6392,7 +6616,7 @@
       <c r="M152" s="6"/>
       <c r="N152" s="6"/>
     </row>
-    <row r="153" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6"/>
       <c r="D153" s="48"/>
       <c r="E153" s="48"/>
@@ -6404,7 +6628,7 @@
       <c r="M153" s="6"/>
       <c r="N153" s="6"/>
     </row>
-    <row r="154" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A154" s="6"/>
       <c r="D154" s="48"/>
       <c r="E154" s="48"/>
@@ -6416,7 +6640,7 @@
       <c r="M154" s="6"/>
       <c r="N154" s="6"/>
     </row>
-    <row r="155" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6"/>
       <c r="D155" s="48"/>
       <c r="E155" s="48"/>
@@ -6428,7 +6652,7 @@
       <c r="M155" s="6"/>
       <c r="N155" s="6"/>
     </row>
-    <row r="156" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="6"/>
       <c r="D156" s="48"/>
       <c r="E156" s="48"/>
@@ -6440,7 +6664,7 @@
       <c r="M156" s="6"/>
       <c r="N156" s="6"/>
     </row>
-    <row r="157" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6"/>
       <c r="D157" s="48"/>
       <c r="E157" s="48"/>
@@ -6452,7 +6676,7 @@
       <c r="M157" s="6"/>
       <c r="N157" s="6"/>
     </row>
-    <row r="158" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A158" s="6"/>
       <c r="D158" s="48"/>
       <c r="E158" s="48"/>
@@ -6464,7 +6688,7 @@
       <c r="M158" s="6"/>
       <c r="N158" s="6"/>
     </row>
-    <row r="159" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A159" s="6"/>
       <c r="D159" s="48"/>
       <c r="E159" s="48"/>
@@ -6476,7 +6700,7 @@
       <c r="M159" s="6"/>
       <c r="N159" s="6"/>
     </row>
-    <row r="160" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A160" s="6"/>
       <c r="D160" s="48"/>
       <c r="E160" s="48"/>
@@ -6488,7 +6712,7 @@
       <c r="M160" s="6"/>
       <c r="N160" s="6"/>
     </row>
-    <row r="161" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6"/>
       <c r="D161" s="48"/>
       <c r="E161" s="48"/>
@@ -6500,7 +6724,7 @@
       <c r="M161" s="6"/>
       <c r="N161" s="6"/>
     </row>
-    <row r="162" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A162" s="6"/>
       <c r="D162" s="48"/>
       <c r="E162" s="48"/>
@@ -6512,7 +6736,7 @@
       <c r="M162" s="6"/>
       <c r="N162" s="6"/>
     </row>
-    <row r="163" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A163" s="6"/>
       <c r="D163" s="48"/>
       <c r="E163" s="48"/>
@@ -6524,7 +6748,7 @@
       <c r="M163" s="6"/>
       <c r="N163" s="6"/>
     </row>
-    <row r="164" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A164" s="6"/>
       <c r="D164" s="48"/>
       <c r="E164" s="48"/>
@@ -6536,7 +6760,7 @@
       <c r="M164" s="6"/>
       <c r="N164" s="6"/>
     </row>
-    <row r="165" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6"/>
       <c r="D165" s="48"/>
       <c r="E165" s="48"/>
@@ -6548,7 +6772,7 @@
       <c r="M165" s="6"/>
       <c r="N165" s="6"/>
     </row>
-    <row r="166" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="6"/>
       <c r="D166" s="48"/>
       <c r="E166" s="48"/>
@@ -6560,7 +6784,7 @@
       <c r="M166" s="6"/>
       <c r="N166" s="6"/>
     </row>
-    <row r="167" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A167" s="6"/>
       <c r="D167" s="48"/>
       <c r="E167" s="48"/>
@@ -6572,7 +6796,7 @@
       <c r="M167" s="6"/>
       <c r="N167" s="6"/>
     </row>
-    <row r="168" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A168" s="6"/>
       <c r="D168" s="48"/>
       <c r="E168" s="48"/>
@@ -6584,7 +6808,7 @@
       <c r="M168" s="6"/>
       <c r="N168" s="6"/>
     </row>
-    <row r="169" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6"/>
       <c r="D169" s="48"/>
       <c r="E169" s="48"/>
@@ -6596,7 +6820,7 @@
       <c r="M169" s="6"/>
       <c r="N169" s="6"/>
     </row>
-    <row r="170" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A170" s="6"/>
       <c r="D170" s="48"/>
       <c r="E170" s="48"/>
@@ -6608,7 +6832,7 @@
       <c r="M170" s="6"/>
       <c r="N170" s="6"/>
     </row>
-    <row r="171" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6"/>
       <c r="D171" s="48"/>
       <c r="E171" s="48"/>
@@ -6620,7 +6844,7 @@
       <c r="M171" s="6"/>
       <c r="N171" s="6"/>
     </row>
-    <row r="172" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A172" s="6"/>
       <c r="D172" s="48"/>
       <c r="E172" s="48"/>
@@ -6632,7 +6856,7 @@
       <c r="M172" s="6"/>
       <c r="N172" s="6"/>
     </row>
-    <row r="173" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6"/>
       <c r="D173" s="48"/>
       <c r="E173" s="48"/>
@@ -6644,7 +6868,7 @@
       <c r="M173" s="6"/>
       <c r="N173" s="6"/>
     </row>
-    <row r="174" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A174" s="6"/>
       <c r="D174" s="48"/>
       <c r="E174" s="48"/>
@@ -6656,7 +6880,7 @@
       <c r="M174" s="6"/>
       <c r="N174" s="6"/>
     </row>
-    <row r="175" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6"/>
       <c r="D175" s="48"/>
       <c r="E175" s="48"/>
@@ -6668,7 +6892,7 @@
       <c r="M175" s="6"/>
       <c r="N175" s="6"/>
     </row>
-    <row r="176" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A176" s="6"/>
       <c r="D176" s="48"/>
       <c r="E176" s="48"/>
@@ -6680,7 +6904,7 @@
       <c r="M176" s="6"/>
       <c r="N176" s="6"/>
     </row>
-    <row r="177" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6"/>
       <c r="D177" s="48"/>
       <c r="E177" s="48"/>
@@ -6692,7 +6916,7 @@
       <c r="M177" s="6"/>
       <c r="N177" s="6"/>
     </row>
-    <row r="178" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A178" s="6"/>
       <c r="D178" s="48"/>
       <c r="E178" s="48"/>
@@ -6704,7 +6928,7 @@
       <c r="M178" s="6"/>
       <c r="N178" s="6"/>
     </row>
-    <row r="179" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:109" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6"/>
       <c r="D179" s="48"/>
       <c r="E179" s="48"/>
@@ -6716,7 +6940,7 @@
       <c r="M179" s="6"/>
       <c r="N179" s="6"/>
     </row>
-    <row r="180" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A180" s="6"/>
       <c r="J180" s="6"/>
       <c r="K180" s="6"/>
@@ -6815,7 +7039,7 @@
       <c r="DD180" s="8"/>
       <c r="DE180" s="8"/>
     </row>
-    <row r="181" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A181" s="6"/>
       <c r="J181" s="6"/>
       <c r="K181" s="6"/>
@@ -6914,7 +7138,7 @@
       <c r="DD181" s="8"/>
       <c r="DE181" s="8"/>
     </row>
-    <row r="182" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A182" s="6"/>
       <c r="J182" s="6"/>
       <c r="K182" s="6"/>
@@ -7013,7 +7237,7 @@
       <c r="DD182" s="8"/>
       <c r="DE182" s="8"/>
     </row>
-    <row r="183" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A183" s="6"/>
       <c r="J183" s="6"/>
       <c r="K183" s="6"/>
@@ -7112,7 +7336,7 @@
       <c r="DD183" s="8"/>
       <c r="DE183" s="8"/>
     </row>
-    <row r="184" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A184" s="6"/>
       <c r="J184" s="6"/>
       <c r="K184" s="6"/>
@@ -7211,7 +7435,7 @@
       <c r="DD184" s="8"/>
       <c r="DE184" s="8"/>
     </row>
-    <row r="185" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A185" s="6"/>
       <c r="J185" s="6"/>
       <c r="K185" s="6"/>
@@ -7310,7 +7534,7 @@
       <c r="DD185" s="8"/>
       <c r="DE185" s="8"/>
     </row>
-    <row r="186" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A186" s="6"/>
       <c r="J186" s="6"/>
       <c r="K186" s="6"/>
@@ -7409,7 +7633,7 @@
       <c r="DD186" s="8"/>
       <c r="DE186" s="8"/>
     </row>
-    <row r="187" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A187" s="6"/>
       <c r="J187" s="6"/>
       <c r="K187" s="6"/>
@@ -7508,7 +7732,7 @@
       <c r="DD187" s="8"/>
       <c r="DE187" s="8"/>
     </row>
-    <row r="188" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A188" s="6"/>
       <c r="J188" s="6"/>
       <c r="K188" s="6"/>
@@ -7607,7 +7831,7 @@
       <c r="DD188" s="8"/>
       <c r="DE188" s="8"/>
     </row>
-    <row r="189" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A189" s="6"/>
       <c r="J189" s="6"/>
       <c r="K189" s="6"/>
@@ -7706,7 +7930,7 @@
       <c r="DD189" s="8"/>
       <c r="DE189" s="8"/>
     </row>
-    <row r="190" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A190" s="6"/>
       <c r="J190" s="6"/>
       <c r="K190" s="6"/>
@@ -7805,7 +8029,7 @@
       <c r="DD190" s="8"/>
       <c r="DE190" s="8"/>
     </row>
-    <row r="191" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A191" s="6"/>
       <c r="J191" s="6"/>
       <c r="K191" s="6"/>
@@ -7904,7 +8128,7 @@
       <c r="DD191" s="8"/>
       <c r="DE191" s="8"/>
     </row>
-    <row r="192" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A192" s="6"/>
       <c r="J192" s="6"/>
       <c r="K192" s="6"/>
@@ -8003,7 +8227,7 @@
       <c r="DD192" s="8"/>
       <c r="DE192" s="8"/>
     </row>
-    <row r="193" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A193" s="6"/>
       <c r="J193" s="6"/>
       <c r="K193" s="6"/>
@@ -8102,7 +8326,7 @@
       <c r="DD193" s="8"/>
       <c r="DE193" s="8"/>
     </row>
-    <row r="194" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A194" s="6"/>
       <c r="J194" s="6"/>
       <c r="K194" s="6"/>
@@ -8201,7 +8425,7 @@
       <c r="DD194" s="8"/>
       <c r="DE194" s="8"/>
     </row>
-    <row r="195" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A195" s="6"/>
       <c r="J195" s="6"/>
       <c r="K195" s="6"/>
@@ -8300,7 +8524,7 @@
       <c r="DD195" s="8"/>
       <c r="DE195" s="8"/>
     </row>
-    <row r="196" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A196" s="6"/>
       <c r="J196" s="6"/>
       <c r="K196" s="6"/>
@@ -8399,7 +8623,7 @@
       <c r="DD196" s="8"/>
       <c r="DE196" s="8"/>
     </row>
-    <row r="197" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A197" s="6"/>
       <c r="J197" s="6"/>
       <c r="K197" s="6"/>
@@ -8498,7 +8722,7 @@
       <c r="DD197" s="8"/>
       <c r="DE197" s="8"/>
     </row>
-    <row r="198" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A198" s="6"/>
       <c r="J198" s="6"/>
       <c r="K198" s="6"/>
@@ -8597,7 +8821,7 @@
       <c r="DD198" s="8"/>
       <c r="DE198" s="8"/>
     </row>
-    <row r="199" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A199" s="6"/>
       <c r="J199" s="6"/>
       <c r="K199" s="6"/>
@@ -8696,7 +8920,7 @@
       <c r="DD199" s="8"/>
       <c r="DE199" s="8"/>
     </row>
-    <row r="200" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A200" s="6"/>
       <c r="J200" s="6"/>
       <c r="K200" s="6"/>
@@ -8794,7 +9018,7 @@
       <c r="DD200" s="8"/>
       <c r="DE200" s="8"/>
     </row>
-    <row r="201" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A201" s="6"/>
       <c r="J201" s="6"/>
       <c r="K201" s="6"/>
@@ -8891,7 +9115,7 @@
       <c r="DD201" s="8"/>
       <c r="DE201" s="8"/>
     </row>
-    <row r="202" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A202" s="6"/>
       <c r="J202" s="6"/>
       <c r="K202" s="6"/>
@@ -8988,7 +9212,7 @@
       <c r="DD202" s="8"/>
       <c r="DE202" s="8"/>
     </row>
-    <row r="203" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A203" s="6"/>
       <c r="J203" s="6"/>
       <c r="K203" s="6"/>
@@ -9085,7 +9309,7 @@
       <c r="DD203" s="8"/>
       <c r="DE203" s="8"/>
     </row>
-    <row r="204" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A204" s="6"/>
       <c r="J204" s="6"/>
       <c r="K204" s="6"/>
@@ -9182,7 +9406,7 @@
       <c r="DD204" s="8"/>
       <c r="DE204" s="8"/>
     </row>
-    <row r="205" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A205" s="6"/>
       <c r="J205" s="6"/>
       <c r="K205" s="6"/>
@@ -9279,7 +9503,7 @@
       <c r="DD205" s="8"/>
       <c r="DE205" s="8"/>
     </row>
-    <row r="206" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A206" s="6"/>
       <c r="S206" s="8"/>
       <c r="T206" s="8"/>
@@ -9373,7 +9597,7 @@
       <c r="DD206" s="8"/>
       <c r="DE206" s="8"/>
     </row>
-    <row r="207" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A207" s="6"/>
       <c r="S207" s="8"/>
       <c r="T207" s="8"/>
@@ -9467,7 +9691,7 @@
       <c r="DD207" s="8"/>
       <c r="DE207" s="8"/>
     </row>
-    <row r="208" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A208" s="6"/>
       <c r="S208" s="8"/>
       <c r="T208" s="8"/>
@@ -9561,7 +9785,7 @@
       <c r="DD208" s="8"/>
       <c r="DE208" s="8"/>
     </row>
-    <row r="209" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A209" s="6"/>
       <c r="S209" s="8"/>
       <c r="T209" s="8"/>
@@ -9655,7 +9879,7 @@
       <c r="DD209" s="8"/>
       <c r="DE209" s="8"/>
     </row>
-    <row r="210" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A210" s="6"/>
       <c r="S210" s="8"/>
       <c r="T210" s="8"/>
@@ -9749,7 +9973,7 @@
       <c r="DD210" s="8"/>
       <c r="DE210" s="8"/>
     </row>
-    <row r="211" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A211" s="6"/>
       <c r="S211" s="8"/>
       <c r="T211" s="8"/>
@@ -9843,7 +10067,7 @@
       <c r="DD211" s="8"/>
       <c r="DE211" s="8"/>
     </row>
-    <row r="212" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A212" s="6"/>
       <c r="S212" s="8"/>
       <c r="T212" s="8"/>
@@ -9937,7 +10161,7 @@
       <c r="DD212" s="8"/>
       <c r="DE212" s="8"/>
     </row>
-    <row r="213" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A213" s="6"/>
       <c r="S213" s="8"/>
       <c r="T213" s="8"/>
@@ -10031,7 +10255,7 @@
       <c r="DD213" s="8"/>
       <c r="DE213" s="8"/>
     </row>
-    <row r="214" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A214" s="6"/>
       <c r="S214" s="8"/>
       <c r="T214" s="8"/>
@@ -10125,7 +10349,7 @@
       <c r="DD214" s="8"/>
       <c r="DE214" s="8"/>
     </row>
-    <row r="215" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A215" s="6"/>
       <c r="S215" s="8"/>
       <c r="T215" s="8"/>
@@ -10219,7 +10443,7 @@
       <c r="DD215" s="8"/>
       <c r="DE215" s="8"/>
     </row>
-    <row r="216" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A216" s="6"/>
       <c r="S216" s="8"/>
       <c r="T216" s="8"/>
@@ -10313,7 +10537,7 @@
       <c r="DD216" s="8"/>
       <c r="DE216" s="8"/>
     </row>
-    <row r="217" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A217" s="6"/>
       <c r="S217" s="8"/>
       <c r="T217" s="8"/>
@@ -10407,7 +10631,7 @@
       <c r="DD217" s="8"/>
       <c r="DE217" s="8"/>
     </row>
-    <row r="218" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A218" s="6"/>
       <c r="S218" s="8"/>
       <c r="T218" s="8"/>
@@ -10501,7 +10725,7 @@
       <c r="DD218" s="8"/>
       <c r="DE218" s="8"/>
     </row>
-    <row r="219" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A219" s="6"/>
       <c r="S219" s="8"/>
       <c r="T219" s="8"/>
@@ -10595,7 +10819,7 @@
       <c r="DD219" s="8"/>
       <c r="DE219" s="8"/>
     </row>
-    <row r="220" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A220" s="6"/>
       <c r="S220" s="8"/>
       <c r="T220" s="8"/>
@@ -10689,7 +10913,7 @@
       <c r="DD220" s="8"/>
       <c r="DE220" s="8"/>
     </row>
-    <row r="221" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A221" s="6"/>
       <c r="S221" s="8"/>
       <c r="T221" s="8"/>
@@ -10783,7 +11007,7 @@
       <c r="DD221" s="8"/>
       <c r="DE221" s="8"/>
     </row>
-    <row r="222" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A222" s="6"/>
       <c r="S222" s="8"/>
       <c r="T222" s="8"/>
@@ -10877,7 +11101,7 @@
       <c r="DD222" s="8"/>
       <c r="DE222" s="8"/>
     </row>
-    <row r="223" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A223" s="6"/>
       <c r="S223" s="8"/>
       <c r="T223" s="8"/>
@@ -10971,7 +11195,7 @@
       <c r="DD223" s="8"/>
       <c r="DE223" s="8"/>
     </row>
-    <row r="224" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A224" s="6"/>
       <c r="S224" s="8"/>
       <c r="T224" s="8"/>
@@ -11065,7 +11289,7 @@
       <c r="DD224" s="8"/>
       <c r="DE224" s="8"/>
     </row>
-    <row r="225" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A225" s="6"/>
       <c r="S225" s="8"/>
       <c r="T225" s="8"/>
@@ -11159,7 +11383,7 @@
       <c r="DD225" s="8"/>
       <c r="DE225" s="8"/>
     </row>
-    <row r="226" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A226" s="6"/>
       <c r="S226" s="8"/>
       <c r="T226" s="8"/>
@@ -11253,7 +11477,7 @@
       <c r="DD226" s="8"/>
       <c r="DE226" s="8"/>
     </row>
-    <row r="227" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A227" s="6"/>
       <c r="S227" s="8"/>
       <c r="T227" s="8"/>
@@ -11347,7 +11571,7 @@
       <c r="DD227" s="8"/>
       <c r="DE227" s="8"/>
     </row>
-    <row r="228" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A228" s="6"/>
       <c r="S228" s="8"/>
       <c r="T228" s="8"/>
@@ -11441,7 +11665,7 @@
       <c r="DD228" s="8"/>
       <c r="DE228" s="8"/>
     </row>
-    <row r="229" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A229" s="6"/>
       <c r="S229" s="8"/>
       <c r="T229" s="8"/>
@@ -11535,7 +11759,7 @@
       <c r="DD229" s="8"/>
       <c r="DE229" s="8"/>
     </row>
-    <row r="230" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A230" s="6"/>
       <c r="S230" s="8"/>
       <c r="T230" s="8"/>
@@ -11629,7 +11853,7 @@
       <c r="DD230" s="8"/>
       <c r="DE230" s="8"/>
     </row>
-    <row r="231" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A231" s="6"/>
       <c r="S231" s="8"/>
       <c r="T231" s="8"/>
@@ -11723,7 +11947,7 @@
       <c r="DD231" s="8"/>
       <c r="DE231" s="8"/>
     </row>
-    <row r="232" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A232" s="6"/>
       <c r="S232" s="8"/>
       <c r="T232" s="8"/>
@@ -11817,7 +12041,7 @@
       <c r="DD232" s="8"/>
       <c r="DE232" s="8"/>
     </row>
-    <row r="233" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A233" s="6"/>
       <c r="S233" s="8"/>
       <c r="T233" s="8"/>
@@ -11911,7 +12135,7 @@
       <c r="DD233" s="8"/>
       <c r="DE233" s="8"/>
     </row>
-    <row r="234" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A234" s="6"/>
       <c r="S234" s="8"/>
       <c r="T234" s="8"/>
@@ -12005,7 +12229,7 @@
       <c r="DD234" s="8"/>
       <c r="DE234" s="8"/>
     </row>
-    <row r="235" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A235" s="6"/>
       <c r="S235" s="8"/>
       <c r="T235" s="8"/>
@@ -12099,7 +12323,7 @@
       <c r="DD235" s="8"/>
       <c r="DE235" s="8"/>
     </row>
-    <row r="236" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A236" s="6"/>
       <c r="S236" s="8"/>
       <c r="T236" s="8"/>
@@ -12193,7 +12417,7 @@
       <c r="DD236" s="8"/>
       <c r="DE236" s="8"/>
     </row>
-    <row r="237" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A237" s="6"/>
       <c r="S237" s="8"/>
       <c r="T237" s="8"/>
@@ -12287,7 +12511,7 @@
       <c r="DD237" s="8"/>
       <c r="DE237" s="8"/>
     </row>
-    <row r="238" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A238" s="6"/>
       <c r="S238" s="8"/>
       <c r="T238" s="8"/>
@@ -12381,7 +12605,7 @@
       <c r="DD238" s="8"/>
       <c r="DE238" s="8"/>
     </row>
-    <row r="239" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A239" s="6"/>
       <c r="S239" s="8"/>
       <c r="T239" s="8"/>
@@ -12475,7 +12699,7 @@
       <c r="DD239" s="8"/>
       <c r="DE239" s="8"/>
     </row>
-    <row r="240" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A240" s="6"/>
       <c r="S240" s="8"/>
       <c r="T240" s="8"/>
@@ -12569,7 +12793,7 @@
       <c r="DD240" s="8"/>
       <c r="DE240" s="8"/>
     </row>
-    <row r="241" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A241" s="6"/>
       <c r="S241" s="8"/>
       <c r="T241" s="8"/>
@@ -12663,7 +12887,7 @@
       <c r="DD241" s="8"/>
       <c r="DE241" s="8"/>
     </row>
-    <row r="242" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A242" s="6"/>
       <c r="S242" s="8"/>
       <c r="T242" s="8"/>
@@ -12757,7 +12981,7 @@
       <c r="DD242" s="8"/>
       <c r="DE242" s="8"/>
     </row>
-    <row r="243" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A243" s="6"/>
       <c r="S243" s="8"/>
       <c r="T243" s="8"/>
@@ -12851,7 +13075,7 @@
       <c r="DD243" s="8"/>
       <c r="DE243" s="8"/>
     </row>
-    <row r="244" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A244" s="6"/>
       <c r="S244" s="8"/>
       <c r="T244" s="8"/>
@@ -12945,7 +13169,7 @@
       <c r="DD244" s="8"/>
       <c r="DE244" s="8"/>
     </row>
-    <row r="245" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A245" s="6"/>
       <c r="S245" s="8"/>
       <c r="T245" s="8"/>
@@ -13039,7 +13263,7 @@
       <c r="DD245" s="8"/>
       <c r="DE245" s="8"/>
     </row>
-    <row r="246" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A246" s="6"/>
       <c r="S246" s="8"/>
       <c r="T246" s="8"/>
@@ -13133,7 +13357,7 @@
       <c r="DD246" s="8"/>
       <c r="DE246" s="8"/>
     </row>
-    <row r="247" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A247" s="6"/>
       <c r="S247" s="8"/>
       <c r="T247" s="8"/>
@@ -13227,7 +13451,7 @@
       <c r="DD247" s="8"/>
       <c r="DE247" s="8"/>
     </row>
-    <row r="248" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A248" s="6"/>
       <c r="S248" s="8"/>
       <c r="T248" s="8"/>
@@ -13321,7 +13545,7 @@
       <c r="DD248" s="8"/>
       <c r="DE248" s="8"/>
     </row>
-    <row r="249" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A249" s="6"/>
       <c r="S249" s="8"/>
       <c r="T249" s="8"/>
@@ -13415,7 +13639,7 @@
       <c r="DD249" s="8"/>
       <c r="DE249" s="8"/>
     </row>
-    <row r="250" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A250" s="6"/>
       <c r="S250" s="8"/>
       <c r="T250" s="8"/>
@@ -13509,7 +13733,7 @@
       <c r="DD250" s="8"/>
       <c r="DE250" s="8"/>
     </row>
-    <row r="251" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A251" s="6"/>
       <c r="S251" s="8"/>
       <c r="T251" s="8"/>
@@ -13603,7 +13827,7 @@
       <c r="DD251" s="8"/>
       <c r="DE251" s="8"/>
     </row>
-    <row r="252" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A252" s="6"/>
       <c r="S252" s="8"/>
       <c r="T252" s="8"/>
@@ -13697,7 +13921,7 @@
       <c r="DD252" s="8"/>
       <c r="DE252" s="8"/>
     </row>
-    <row r="253" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A253" s="6"/>
       <c r="S253" s="8"/>
       <c r="T253" s="8"/>
@@ -13791,7 +14015,7 @@
       <c r="DD253" s="8"/>
       <c r="DE253" s="8"/>
     </row>
-    <row r="254" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A254" s="6"/>
       <c r="S254" s="8"/>
       <c r="T254" s="8"/>
@@ -13885,7 +14109,7 @@
       <c r="DD254" s="8"/>
       <c r="DE254" s="8"/>
     </row>
-    <row r="255" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A255" s="6"/>
       <c r="S255" s="8"/>
       <c r="T255" s="8"/>
@@ -13979,7 +14203,7 @@
       <c r="DD255" s="8"/>
       <c r="DE255" s="8"/>
     </row>
-    <row r="256" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A256" s="6"/>
       <c r="S256" s="8"/>
       <c r="T256" s="8"/>
@@ -14073,7 +14297,7 @@
       <c r="DD256" s="8"/>
       <c r="DE256" s="8"/>
     </row>
-    <row r="257" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A257" s="6"/>
       <c r="S257" s="8"/>
       <c r="T257" s="8"/>
@@ -14167,7 +14391,7 @@
       <c r="DD257" s="8"/>
       <c r="DE257" s="8"/>
     </row>
-    <row r="258" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A258" s="6"/>
       <c r="S258" s="8"/>
       <c r="T258" s="8"/>
@@ -14261,7 +14485,7 @@
       <c r="DD258" s="8"/>
       <c r="DE258" s="8"/>
     </row>
-    <row r="259" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A259" s="6"/>
       <c r="S259" s="8"/>
       <c r="T259" s="8"/>
@@ -14355,7 +14579,7 @@
       <c r="DD259" s="8"/>
       <c r="DE259" s="8"/>
     </row>
-    <row r="260" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:109" x14ac:dyDescent="0.2">
       <c r="A260" s="6"/>
       <c r="S260" s="8"/>
       <c r="T260" s="8"/>
@@ -14449,7 +14673,7 @@
       <c r="DD260" s="8"/>
       <c r="DE260" s="8"/>
     </row>
-    <row r="261" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S261" s="8"/>
       <c r="T261" s="8"/>
       <c r="U261" s="8"/>
@@ -14542,7 +14766,7 @@
       <c r="DD261" s="8"/>
       <c r="DE261" s="8"/>
     </row>
-    <row r="262" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S262" s="8"/>
       <c r="T262" s="8"/>
       <c r="U262" s="8"/>
@@ -14635,7 +14859,7 @@
       <c r="DD262" s="8"/>
       <c r="DE262" s="8"/>
     </row>
-    <row r="263" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S263" s="8"/>
       <c r="T263" s="8"/>
       <c r="U263" s="8"/>
@@ -14728,7 +14952,7 @@
       <c r="DD263" s="8"/>
       <c r="DE263" s="8"/>
     </row>
-    <row r="264" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S264" s="8"/>
       <c r="T264" s="8"/>
       <c r="U264" s="8"/>
@@ -14821,7 +15045,7 @@
       <c r="DD264" s="8"/>
       <c r="DE264" s="8"/>
     </row>
-    <row r="265" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S265" s="8"/>
       <c r="T265" s="8"/>
       <c r="U265" s="8"/>
@@ -14914,7 +15138,7 @@
       <c r="DD265" s="8"/>
       <c r="DE265" s="8"/>
     </row>
-    <row r="266" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S266" s="8"/>
       <c r="T266" s="8"/>
       <c r="U266" s="8"/>
@@ -15007,7 +15231,7 @@
       <c r="DD266" s="8"/>
       <c r="DE266" s="8"/>
     </row>
-    <row r="267" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S267" s="8"/>
       <c r="T267" s="8"/>
       <c r="U267" s="8"/>
@@ -15100,7 +15324,7 @@
       <c r="DD267" s="8"/>
       <c r="DE267" s="8"/>
     </row>
-    <row r="268" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S268" s="8"/>
       <c r="T268" s="8"/>
       <c r="U268" s="8"/>
@@ -15193,7 +15417,7 @@
       <c r="DD268" s="8"/>
       <c r="DE268" s="8"/>
     </row>
-    <row r="269" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S269" s="8"/>
       <c r="T269" s="8"/>
       <c r="U269" s="8"/>
@@ -15286,7 +15510,7 @@
       <c r="DD269" s="8"/>
       <c r="DE269" s="8"/>
     </row>
-    <row r="270" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S270" s="8"/>
       <c r="T270" s="8"/>
       <c r="U270" s="8"/>
@@ -15379,7 +15603,7 @@
       <c r="DD270" s="8"/>
       <c r="DE270" s="8"/>
     </row>
-    <row r="271" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S271" s="8"/>
       <c r="T271" s="8"/>
       <c r="U271" s="8"/>
@@ -15472,7 +15696,7 @@
       <c r="DD271" s="8"/>
       <c r="DE271" s="8"/>
     </row>
-    <row r="272" spans="1:109" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:109" x14ac:dyDescent="0.2">
       <c r="S272" s="8"/>
       <c r="T272" s="8"/>
       <c r="U272" s="8"/>
@@ -15565,7 +15789,7 @@
       <c r="DD272" s="8"/>
       <c r="DE272" s="8"/>
     </row>
-    <row r="273" spans="19:109" x14ac:dyDescent="0.3">
+    <row r="273" spans="19:109" x14ac:dyDescent="0.2">
       <c r="S273" s="8"/>
       <c r="T273" s="8"/>
       <c r="U273" s="8"/>
@@ -15658,7 +15882,7 @@
       <c r="DD273" s="8"/>
       <c r="DE273" s="8"/>
     </row>
-    <row r="274" spans="19:109" x14ac:dyDescent="0.3">
+    <row r="274" spans="19:109" x14ac:dyDescent="0.2">
       <c r="S274" s="8"/>
       <c r="T274" s="8"/>
       <c r="U274" s="8"/>
@@ -15751,7 +15975,7 @@
       <c r="DD274" s="8"/>
       <c r="DE274" s="8"/>
     </row>
-    <row r="275" spans="19:109" x14ac:dyDescent="0.3">
+    <row r="275" spans="19:109" x14ac:dyDescent="0.2">
       <c r="S275" s="8"/>
       <c r="T275" s="8"/>
       <c r="U275" s="8"/>
@@ -15844,7 +16068,7 @@
       <c r="DD275" s="8"/>
       <c r="DE275" s="8"/>
     </row>
-    <row r="276" spans="19:109" x14ac:dyDescent="0.3">
+    <row r="276" spans="19:109" x14ac:dyDescent="0.2">
       <c r="S276" s="8"/>
       <c r="T276" s="8"/>
       <c r="U276" s="8"/>
@@ -15937,7 +16161,7 @@
       <c r="DD276" s="8"/>
       <c r="DE276" s="8"/>
     </row>
-    <row r="277" spans="19:109" x14ac:dyDescent="0.3">
+    <row r="277" spans="19:109" x14ac:dyDescent="0.2">
       <c r="S277" s="8"/>
       <c r="T277" s="8"/>
       <c r="U277" s="8"/>
@@ -16045,24 +16269,24 @@
     <sortCondition ref="B4:B103"/>
   </sortState>
   <conditionalFormatting sqref="J1">
-    <cfRule type="containsBlanks" dxfId="5" priority="258">
+    <cfRule type="containsBlanks" dxfId="6" priority="258">
       <formula>LEN(TRIM(J1))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="259" operator="containsText" text="Nein">
+    <cfRule type="containsText" dxfId="5" priority="259" operator="containsText" text="Nein">
       <formula>NOT(ISERROR(SEARCH("Nein",J1)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="260">
+    <cfRule type="expression" dxfId="4" priority="260">
       <formula>"Nein"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P10:Q10">
-    <cfRule type="expression" dxfId="2" priority="11">
+    <cfRule type="expression" dxfId="3" priority="11">
       <formula>COUNTIF($B10,"*x*")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="12">
+    <cfRule type="expression" dxfId="2" priority="12">
       <formula>IF(AND($M10&gt;0,$M10&lt;101),TRUE,FALSE)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="13">
+    <cfRule type="expression" dxfId="1" priority="13">
       <formula>COUNTIF($L10,"*mj*")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16116,28 +16340,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED9F3C5-25A3-4129-A737-A1791F16FEA7}">
   <dimension ref="A3:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="50" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="51" t="s">
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="3">
